--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F3BB58-36F5-4AA9-A21F-C08E53B4010C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8123D-CA87-410D-9663-E09698BD6636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="216">
   <si>
     <t>##var</t>
   </si>
@@ -878,6 +878,42 @@
   </si>
   <si>
     <t>鳞片间流动着细小的时间刻度，据说凝视它太久，会想起一段已经遗忘的往事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_04_redtail_carp]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_05_grass_carp]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_06_silver_carp]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_07_river_perch]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_08_mandarin_fish]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_09_blue_catfish]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_10_lucky_koi]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_11_moonlight_trout]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_12_timefish]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2608,6 +2644,9 @@
       <c r="F55" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="G55" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56">
@@ -2625,6 +2664,9 @@
       <c r="F56" s="1" t="s">
         <v>199</v>
       </c>
+      <c r="G56" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57">
@@ -2642,6 +2684,9 @@
       <c r="F57" s="1" t="s">
         <v>200</v>
       </c>
+      <c r="G57" s="1" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58">
@@ -2659,6 +2704,9 @@
       <c r="F58" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="G58" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59">
@@ -2676,6 +2724,9 @@
       <c r="F59" s="1" t="s">
         <v>202</v>
       </c>
+      <c r="G59" s="1" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60">
@@ -2693,6 +2744,9 @@
       <c r="F60" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="G60" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61">
@@ -2710,6 +2764,9 @@
       <c r="F61" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="G61" s="1" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62">
@@ -2727,6 +2784,9 @@
       <c r="F62" s="1" t="s">
         <v>205</v>
       </c>
+      <c r="G62" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63">
@@ -2743,6 +2803,9 @@
       </c>
       <c r="F63" s="1" t="s">
         <v>206</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8123D-CA87-410D-9663-E09698BD6636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497AC7B6-40E1-4FC0-9F78-776AF7B6E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -915,6 +915,90 @@
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_12_timefish]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵巧细钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宽口鱼钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稳固倒刺钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双重稳固钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光鱼钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蚯蚓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉米</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小虾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫金果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>练习圆钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_01_beginner]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_02_agile]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_03_wide]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_04_barbed]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_05_double]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_06_time]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_time]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_scent_fruit]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_corn]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_dough]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_worm]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_shrimp]</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -2647,6 +2731,9 @@
       <c r="G55" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="I55">
+        <v>5000</v>
+      </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56">
@@ -2667,6 +2754,9 @@
       <c r="G56" s="1" t="s">
         <v>208</v>
       </c>
+      <c r="I56">
+        <v>5000</v>
+      </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57">
@@ -2687,6 +2777,9 @@
       <c r="G57" s="1" t="s">
         <v>209</v>
       </c>
+      <c r="I57">
+        <v>5000</v>
+      </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58">
@@ -2707,6 +2800,9 @@
       <c r="G58" s="1" t="s">
         <v>210</v>
       </c>
+      <c r="I58">
+        <v>5000</v>
+      </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59">
@@ -2727,6 +2823,9 @@
       <c r="G59" s="1" t="s">
         <v>211</v>
       </c>
+      <c r="I59">
+        <v>5000</v>
+      </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60">
@@ -2747,6 +2846,9 @@
       <c r="G60" s="1" t="s">
         <v>212</v>
       </c>
+      <c r="I60">
+        <v>5000</v>
+      </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61">
@@ -2767,6 +2869,9 @@
       <c r="G61" s="1" t="s">
         <v>213</v>
       </c>
+      <c r="I61">
+        <v>5000</v>
+      </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62">
@@ -2787,6 +2892,9 @@
       <c r="G62" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="I62">
+        <v>5000</v>
+      </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63">
@@ -2806,6 +2914,287 @@
       </c>
       <c r="G63" s="1" t="s">
         <v>215</v>
+      </c>
+      <c r="I63">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B64">
+        <v>6020</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>6</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G64" t="s">
+        <v>229</v>
+      </c>
+      <c r="I64">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B65">
+        <v>6021</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <v>6</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G65" t="s">
+        <v>230</v>
+      </c>
+      <c r="I65">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B66">
+        <v>6022</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G66" t="s">
+        <v>231</v>
+      </c>
+      <c r="I66">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B67">
+        <v>6023</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>6</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G67" t="s">
+        <v>232</v>
+      </c>
+      <c r="I67">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B68">
+        <v>6024</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G68" t="s">
+        <v>233</v>
+      </c>
+      <c r="I68">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B69">
+        <v>6025</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>6</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G69" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B70">
+        <v>6030</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G70" t="s">
+        <v>237</v>
+      </c>
+      <c r="I70">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B71">
+        <v>6031</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G71" t="s">
+        <v>238</v>
+      </c>
+      <c r="I71">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B72">
+        <v>6032</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>6</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G72" t="s">
+        <v>236</v>
+      </c>
+      <c r="I72">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B73">
+        <v>6033</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>6</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G73" t="s">
+        <v>239</v>
+      </c>
+      <c r="I73">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B74">
+        <v>6034</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G74" t="s">
+        <v>235</v>
+      </c>
+      <c r="I74">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B75">
+        <v>6035</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+      <c r="E75">
+        <v>6</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G75" t="s">
+        <v>234</v>
+      </c>
+      <c r="I75">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I76">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497AC7B6-40E1-4FC0-9F78-776AF7B6E66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F290AEC4-6DA2-411C-BED9-FF60E41ACF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1354,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -2930,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>216</v>
@@ -2953,7 +2953,7 @@
         <v>2</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>217</v>
@@ -2976,7 +2976,7 @@
         <v>3</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>218</v>
@@ -2999,7 +2999,7 @@
         <v>4</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>219</v>
@@ -3022,7 +3022,7 @@
         <v>5</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>220</v>
@@ -3045,13 +3045,16 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>227</v>
       </c>
       <c r="G69" t="s">
         <v>228</v>
+      </c>
+      <c r="I69">
+        <v>5000</v>
       </c>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.2">
@@ -3065,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>221</v>
@@ -3088,7 +3091,7 @@
         <v>2</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>222</v>
@@ -3111,7 +3114,7 @@
         <v>2</v>
       </c>
       <c r="E72">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>223</v>
@@ -3134,7 +3137,7 @@
         <v>3</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>224</v>
@@ -3157,7 +3160,7 @@
         <v>4</v>
       </c>
       <c r="E74">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>225</v>
@@ -3180,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="E75">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>226</v>
@@ -3189,11 +3192,6 @@
         <v>234</v>
       </c>
       <c r="I75">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="I76">
         <v>5000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F290AEC4-6DA2-411C-BED9-FF60E41ACF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17243870-389E-44D6-9DA7-A899990C042C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="243">
   <si>
     <t>##var</t>
   </si>
@@ -999,6 +999,17 @@
   </si>
   <si>
     <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_shrimp]</t>
+  </si>
+  <si>
+    <t>星阵币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘟嘟嘟，星阵币！！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_time_core_matrix_token]</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -1718,51 +1729,45 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13">
-        <v>1050</v>
+        <v>1013</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="I13">
         <v>4000</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>154</v>
-      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1771,27 +1776,27 @@
         <v>4000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1800,76 +1805,76 @@
         <v>4000</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16">
-        <v>2000</v>
+        <v>1052</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16">
         <v>1</v>
       </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>23</v>
+        <v>153</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>3200</v>
+        <v>4000</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I17">
-        <v>4200</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>143</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D18" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>142</v>
@@ -1880,39 +1885,45 @@
       <c r="I18">
         <v>4200</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>174</v>
+      <c r="J18" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19">
-        <v>4000</v>
+        <v>3001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>53</v>
+        <v>142</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>4000</v>
+        <v>4200</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -1921,10 +1932,10 @@
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20">
         <v>4000</v>
@@ -1932,22 +1943,22 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I21">
         <v>4000</v>
@@ -1955,22 +1966,22 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
         <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="I22">
         <v>4000</v>
@@ -1978,10 +1989,10 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
@@ -1990,10 +2001,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I23">
         <v>4000</v>
@@ -2001,33 +2012,33 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" t="s">
-        <v>112</v>
+        <v>73</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="I24">
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2036,33 +2047,33 @@
         <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>115</v>
+        <v>74</v>
+      </c>
+      <c r="G25" t="s">
+        <v>112</v>
       </c>
       <c r="I25">
-        <v>4500</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I26">
         <v>4500</v>
@@ -2070,33 +2081,33 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I27">
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
@@ -2105,10 +2116,10 @@
         <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G28" t="s">
-        <v>117</v>
+        <v>77</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="I28">
         <v>4000</v>
@@ -2116,22 +2127,22 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>117</v>
       </c>
       <c r="I29">
         <v>4000</v>
@@ -2139,10 +2150,10 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -2151,10 +2162,10 @@
         <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I30">
         <v>4000</v>
@@ -2162,22 +2173,22 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
+        <v>68</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
       </c>
       <c r="E31">
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I31">
         <v>4000</v>
@@ -2185,22 +2196,22 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32">
         <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I32">
         <v>4000</v>
@@ -2208,10 +2219,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -2220,44 +2231,44 @@
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I33">
-        <v>4200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I34">
-        <v>4400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -2266,33 +2277,33 @@
         <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G35" t="s">
-        <v>122</v>
+        <v>94</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="I35">
-        <v>4000</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36">
         <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
+      </c>
+      <c r="G36" t="s">
+        <v>122</v>
       </c>
       <c r="I36">
         <v>4000</v>
@@ -2300,33 +2311,33 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I37">
-        <v>5500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2335,10 +2346,10 @@
         <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I38">
         <v>5500</v>
@@ -2346,33 +2357,33 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I39">
-        <v>4500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2381,10 +2392,10 @@
         <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I40">
         <v>4500</v>
@@ -2392,22 +2403,22 @@
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I41">
         <v>4500</v>
@@ -2415,33 +2426,33 @@
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
         <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I42">
-        <v>5000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -2450,44 +2461,44 @@
         <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G43" t="s">
-        <v>132</v>
+        <v>107</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="I43">
-        <v>5500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>134</v>
+        <v>108</v>
+      </c>
+      <c r="G44" t="s">
+        <v>132</v>
       </c>
       <c r="I44">
-        <v>5000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2496,67 +2507,67 @@
         <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I45">
-        <v>5200</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46">
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I46">
-        <v>5500</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47">
-        <v>5000</v>
+        <v>4027</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="I47">
-        <v>6000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -2565,10 +2576,10 @@
         <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I48">
         <v>6000</v>
@@ -2576,10 +2587,10 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -2588,10 +2599,10 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G49" t="s">
-        <v>167</v>
+        <v>164</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="I49">
         <v>6000</v>
@@ -2599,10 +2610,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2611,21 +2622,21 @@
         <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I50">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2634,44 +2645,44 @@
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G51" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I51">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52">
+        <v>5004</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G52" t="s">
+        <v>178</v>
+      </c>
+      <c r="I52">
         <v>6000</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>6</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I52">
-        <v>5000</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2680,10 +2691,10 @@
         <v>6</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I53">
         <v>5000</v>
@@ -2691,10 +2702,10 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2703,10 +2714,10 @@
         <v>6</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I54">
         <v>5000</v>
@@ -2714,22 +2725,22 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55">
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I55">
         <v>5000</v>
@@ -2737,10 +2748,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2749,10 +2760,10 @@
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I56">
         <v>5000</v>
@@ -2760,10 +2771,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2772,10 +2783,10 @@
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I57">
         <v>5000</v>
@@ -2783,22 +2794,22 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58">
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I58">
         <v>5000</v>
@@ -2806,10 +2817,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -2818,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I59">
         <v>5000</v>
@@ -2829,10 +2840,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -2841,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I60">
         <v>5000</v>
@@ -2852,22 +2863,22 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61">
         <v>6</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I61">
         <v>5000</v>
@@ -2875,10 +2886,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -2887,10 +2898,10 @@
         <v>6</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I62">
         <v>5000</v>
@@ -2898,22 +2909,22 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63">
         <v>6</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I63">
         <v>5000</v>
@@ -2921,22 +2932,22 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G64" t="s">
-        <v>229</v>
+        <v>206</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="I64">
         <v>5000</v>
@@ -2944,22 +2955,22 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65">
         <v>7</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I65">
         <v>5000</v>
@@ -2967,22 +2978,22 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I66">
         <v>5000</v>
@@ -2990,22 +3001,22 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E67">
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I67">
         <v>5000</v>
@@ -3013,22 +3024,22 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E68">
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I68">
         <v>5000</v>
@@ -3036,22 +3047,22 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69">
         <v>7</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G69" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I69">
         <v>5000</v>
@@ -3059,22 +3070,22 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>6030</v>
+        <v>6025</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
       <c r="E70">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G70" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I70">
         <v>5000</v>
@@ -3082,22 +3093,22 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G71" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I71">
         <v>5000</v>
@@ -3105,10 +3116,10 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3117,10 +3128,10 @@
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G72" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I72">
         <v>5000</v>
@@ -3128,22 +3139,22 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73">
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G73" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I73">
         <v>5000</v>
@@ -3151,22 +3162,22 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G74" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I74">
         <v>5000</v>
@@ -3174,24 +3185,47 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75">
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G75" t="s">
+        <v>235</v>
+      </c>
+      <c r="I75">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B76">
+        <v>6035</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G75" t="s">
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G76" t="s">
         <v>234</v>
       </c>
-      <c r="I75">
+      <c r="I76">
         <v>5000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17243870-389E-44D6-9DA7-A899990C042C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838F6E92-3042-4550-A9E4-E175EACEE1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,6 +1010,7 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_time_core_matrix_token]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838F6E92-3042-4550-A9E4-E175EACEE1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B84D81-566C-41CC-A051-24665F840875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="246">
   <si>
     <t>##var</t>
   </si>
@@ -1010,6 +1010,17 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_time_core_matrix_token]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60cm巨无霸，超长长长长长长长长长长长长蛋挞！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[item_extra_long_egg_tart]</t>
+  </si>
+  <si>
+    <t>超长长长蛋挞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1366,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -2680,33 +2691,33 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53">
+        <v>5005</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G53" t="s">
+        <v>244</v>
+      </c>
+      <c r="I53">
         <v>6000</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>6</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I53">
-        <v>5000</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2715,10 +2726,10 @@
         <v>6</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I54">
         <v>5000</v>
@@ -2726,10 +2737,10 @@
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2738,10 +2749,10 @@
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I55">
         <v>5000</v>
@@ -2749,22 +2760,22 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I56">
         <v>5000</v>
@@ -2772,10 +2783,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2784,10 +2795,10 @@
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I57">
         <v>5000</v>
@@ -2795,10 +2806,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2807,10 +2818,10 @@
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I58">
         <v>5000</v>
@@ -2818,22 +2829,22 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I59">
         <v>5000</v>
@@ -2841,10 +2852,10 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -2853,10 +2864,10 @@
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I60">
         <v>5000</v>
@@ -2864,10 +2875,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2876,10 +2887,10 @@
         <v>6</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I61">
         <v>5000</v>
@@ -2887,22 +2898,22 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>6</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I62">
         <v>5000</v>
@@ -2910,10 +2921,10 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -2922,10 +2933,10 @@
         <v>6</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I63">
         <v>5000</v>
@@ -2933,22 +2944,22 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64">
         <v>6</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I64">
         <v>5000</v>
@@ -2956,22 +2967,22 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G65" t="s">
-        <v>229</v>
+        <v>206</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="I65">
         <v>5000</v>
@@ -2979,22 +2990,22 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G66" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I66">
         <v>5000</v>
@@ -3002,22 +3013,22 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67">
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G67" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I67">
         <v>5000</v>
@@ -3025,22 +3036,22 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E68">
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I68">
         <v>5000</v>
@@ -3048,22 +3059,22 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69">
         <v>7</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I69">
         <v>5000</v>
@@ -3071,22 +3082,22 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70">
         <v>7</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G70" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I70">
         <v>5000</v>
@@ -3094,22 +3105,22 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>6030</v>
+        <v>6025</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G71" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I71">
         <v>5000</v>
@@ -3117,22 +3128,22 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G72" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I72">
         <v>5000</v>
@@ -3140,10 +3151,10 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3152,10 +3163,10 @@
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G73" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I73">
         <v>5000</v>
@@ -3163,22 +3174,22 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G74" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I74">
         <v>5000</v>
@@ -3186,22 +3197,22 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75">
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G75" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I75">
         <v>5000</v>
@@ -3209,24 +3220,47 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E76">
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G76" t="s">
+        <v>235</v>
+      </c>
+      <c r="I76">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B77">
+        <v>6035</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G76" t="s">
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>8</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G77" t="s">
         <v>234</v>
       </c>
-      <c r="I76">
+      <c r="I77">
         <v>5000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B84D81-566C-41CC-A051-24665F840875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F0DFDD-A0EB-4C6F-9AAD-7FDE9161BE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="249">
   <si>
     <t>##var</t>
   </si>
@@ -1022,6 +1022,17 @@
   <si>
     <t>超长长长蛋挞</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地铁卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有了这张卡，就可以去你想去的地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[time_chip_metro_card]</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
@@ -2576,33 +2587,33 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48">
-        <v>5000</v>
+        <v>4028</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="I48">
-        <v>6000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -2611,10 +2622,10 @@
         <v>5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I49">
         <v>6000</v>
@@ -2622,10 +2633,10 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2634,10 +2645,10 @@
         <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G50" t="s">
-        <v>167</v>
+        <v>164</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="I50">
         <v>6000</v>
@@ -2645,10 +2656,10 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2657,21 +2668,21 @@
         <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G51" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I51">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -2680,33 +2691,33 @@
         <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I52">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53">
-        <v>5005</v>
+        <v>5004</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>5</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="G53" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="I53">
         <v>6000</v>
@@ -2714,33 +2725,33 @@
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54">
+        <v>5005</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G54" t="s">
+        <v>244</v>
+      </c>
+      <c r="I54">
         <v>6000</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>6</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I54">
-        <v>5000</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2749,10 +2760,10 @@
         <v>6</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I55">
         <v>5000</v>
@@ -2760,10 +2771,10 @@
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2772,10 +2783,10 @@
         <v>6</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I56">
         <v>5000</v>
@@ -2783,22 +2794,22 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <v>6</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="I57">
         <v>5000</v>
@@ -2806,10 +2817,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -2818,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I58">
         <v>5000</v>
@@ -2829,10 +2840,10 @@
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -2841,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I59">
         <v>5000</v>
@@ -2852,22 +2863,22 @@
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60">
         <v>6</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I60">
         <v>5000</v>
@@ -2875,10 +2886,10 @@
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2887,10 +2898,10 @@
         <v>6</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I61">
         <v>5000</v>
@@ -2898,10 +2909,10 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -2910,10 +2921,10 @@
         <v>6</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I62">
         <v>5000</v>
@@ -2921,22 +2932,22 @@
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63">
         <v>6</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I63">
         <v>5000</v>
@@ -2944,10 +2955,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -2956,10 +2967,10 @@
         <v>6</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I64">
         <v>5000</v>
@@ -2967,22 +2978,22 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E65">
         <v>6</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I65">
         <v>5000</v>
@@ -2990,22 +3001,22 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G66" t="s">
-        <v>229</v>
+        <v>206</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="I66">
         <v>5000</v>
@@ -3013,22 +3024,22 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I67">
         <v>5000</v>
@@ -3036,22 +3047,22 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>7</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I68">
         <v>5000</v>
@@ -3059,22 +3070,22 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69">
         <v>7</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I69">
         <v>5000</v>
@@ -3082,22 +3093,22 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E70">
         <v>7</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G70" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I70">
         <v>5000</v>
@@ -3105,22 +3116,22 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71">
         <v>7</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G71" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I71">
         <v>5000</v>
@@ -3128,22 +3139,22 @@
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>6030</v>
+        <v>6025</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G72" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I72">
         <v>5000</v>
@@ -3151,22 +3162,22 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G73" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I73">
         <v>5000</v>
@@ -3174,10 +3185,10 @@
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3186,10 +3197,10 @@
         <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G74" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I74">
         <v>5000</v>
@@ -3197,22 +3208,22 @@
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G75" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I75">
         <v>5000</v>
@@ -3220,22 +3231,22 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76">
         <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I76">
         <v>5000</v>
@@ -3243,24 +3254,47 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77">
         <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G77" t="s">
+        <v>235</v>
+      </c>
+      <c r="I77">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B78">
+        <v>6035</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G77" t="s">
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>8</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G78" t="s">
         <v>234</v>
       </c>
-      <c r="I77">
+      <c r="I78">
         <v>5000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F0DFDD-A0EB-4C6F-9AAD-7FDE9161BE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D11250C-30C1-467D-A662-ACC743DEEE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="263">
   <si>
     <t>##var</t>
   </si>
@@ -270,18 +270,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>101,10000,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>101,100,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>101,500,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1033,6 +1025,70 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[time_chip_metro_card]</t>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>健康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>零工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地铁站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼获</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼钩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼饵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,300,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,2000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1388,23 +1444,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K78"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L78"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="79.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="181.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="79.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="74.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1415,29 +1472,32 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" t="s">
-        <v>175</v>
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="F1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1448,29 +1508,32 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>16</v>
+      <c r="H2" t="s">
+        <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1481,10 +1544,10 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+        <v>58</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -1492,18 +1555,21 @@
       <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
+      <c r="H3" t="s">
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1514,29 +1580,32 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1546,26 +1615,29 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>2500</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K5" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1575,26 +1647,29 @@
       <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>3000</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K6" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1604,26 +1679,29 @@
       <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>4000</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1633,26 +1711,29 @@
       <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>4000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1662,26 +1743,29 @@
       <c r="D9" s="1">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>3200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1691,176 +1775,197 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10">
+      <c r="H10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10">
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="1">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11">
+      <c r="J11">
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1012</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D12" s="1">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I12">
+      <c r="J12">
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1013</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I13">
+        <v>239</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J13">
         <v>4000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1050</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H14">
+        <v>144</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>4000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1051</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F15">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H15">
+        <v>146</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>4000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1052</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F16">
         <v>1</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H16">
+        <v>148</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>4000</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K16" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2000</v>
       </c>
@@ -1870,1431 +1975,1617 @@
       <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17">
         <v>2</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>3200</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3000</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D18" s="1">
-        <v>4</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>4200</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>4200</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>3001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19">
         <v>3</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H19">
+        <v>171</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19">
         <v>1</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>4200</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="K19" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>4000</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="E20">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20">
+      <c r="J20">
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>4001</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="E21">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>56</v>
+      <c r="E21" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I21">
+      <c r="H21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21">
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>4002</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
       </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>57</v>
+      <c r="E22" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I22">
+      <c r="H22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22">
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>4003</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
-      <c r="E23">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>72</v>
+      <c r="E23" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23">
+        <v>70</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>4004</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
       </c>
-      <c r="E24">
-        <v>4</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>73</v>
+      <c r="E24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24">
+        <v>71</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J24">
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>4005</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25">
+      <c r="E25" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25">
         <v>3800</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>4006</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
-      <c r="E26">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>75</v>
+      <c r="E26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26">
+        <v>73</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J26">
         <v>4500</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>4007</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D27" s="1">
         <v>4</v>
       </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>76</v>
+      <c r="E27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I27">
+        <v>74</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27">
         <v>4500</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>4008</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>77</v>
+      <c r="E28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28">
+        <v>75</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J28">
         <v>4000</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>4009</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" t="s">
-        <v>117</v>
-      </c>
-      <c r="I29">
+      <c r="E29" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29">
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>4010</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
       </c>
-      <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>79</v>
+      <c r="E30" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I30">
+        <v>77</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J30">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>4011</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
       </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>81</v>
+      <c r="E31" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I31">
+        <v>79</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J31">
         <v>4000</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>4012</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>80</v>
+      <c r="E32" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32">
+        <v>78</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32">
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>4013</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33">
-        <v>4</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>92</v>
+      <c r="E33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I33">
+        <v>90</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J33">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>4014</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
-      <c r="E34">
-        <v>4</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>93</v>
+      <c r="E34" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I34">
+        <v>91</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J34">
         <v>4200</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>4015</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="E35">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>94</v>
+      <c r="E35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35">
+        <v>92</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J35">
         <v>4400</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>4016</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="E36">
-        <v>4</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36">
+      <c r="E36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" t="s">
+        <v>120</v>
+      </c>
+      <c r="J36">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>4017</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>96</v>
+      <c r="E37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I37">
+        <v>94</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J37">
         <v>4000</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>4018</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D38">
         <v>2</v>
       </c>
-      <c r="E38">
-        <v>4</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>97</v>
+      <c r="E38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I38">
+        <v>95</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38">
         <v>5500</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>4019</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
-      <c r="E39">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>98</v>
+      <c r="E39" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I39">
+        <v>96</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J39">
         <v>5500</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>4020</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40">
-        <v>4</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>99</v>
+      <c r="E40" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I40">
+        <v>97</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J40">
         <v>4500</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>4021</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="E41">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>100</v>
+      <c r="E41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I41">
+        <v>98</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J41">
         <v>4500</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>4022</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
-      <c r="E42">
-        <v>4</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>101</v>
+      <c r="E42" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I42">
+        <v>99</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J42">
         <v>4500</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>4023</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="E43">
-        <v>4</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>107</v>
+      <c r="E43" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I43">
+        <v>105</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J43">
         <v>5000</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>4024</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
-      <c r="E44">
-        <v>4</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G44" t="s">
-        <v>132</v>
-      </c>
-      <c r="I44">
+      <c r="E44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" t="s">
+        <v>130</v>
+      </c>
+      <c r="J44">
         <v>5500</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>4025</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
-      <c r="E45">
-        <v>4</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>109</v>
+      <c r="E45" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I45">
+        <v>107</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J45">
         <v>5000</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>4026</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>110</v>
+      <c r="E46" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I46">
+        <v>108</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J46">
         <v>5200</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>4027</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47">
         <v>5</v>
       </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>111</v>
+      <c r="E47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I47">
+        <v>109</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J47">
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>4028</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
-      <c r="E48">
-        <v>4</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>247</v>
+      <c r="E48" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I48">
+        <v>245</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J48">
         <v>5000</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>5000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F49">
         <v>5</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I49">
+        <v>159</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J49">
         <v>6000</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>5001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D50">
         <v>3</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F50">
         <v>5</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I50">
+        <v>162</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J50">
         <v>6000</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>5002</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F51">
         <v>5</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G51" t="s">
-        <v>167</v>
-      </c>
-      <c r="I51">
+      <c r="G51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J51">
         <v>6000</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>5003</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F52">
         <v>5</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G52" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52">
+      <c r="G52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H52" t="s">
+        <v>169</v>
+      </c>
+      <c r="J52">
         <v>7000</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>5004</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F53">
         <v>5</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G53" t="s">
-        <v>178</v>
-      </c>
-      <c r="I53">
+      <c r="G53" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" t="s">
+        <v>176</v>
+      </c>
+      <c r="J53">
         <v>6000</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>5005</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F54">
         <v>5</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G54" t="s">
-        <v>244</v>
-      </c>
-      <c r="I54">
+      <c r="G54" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H54" t="s">
+        <v>242</v>
+      </c>
+      <c r="J54">
         <v>6000</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>6000</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F55">
         <v>6</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I55">
+      <c r="H55" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J55">
         <v>5000</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>6001</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F56">
         <v>6</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I56">
+        <v>182</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J56">
         <v>5000</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>6002</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F57">
         <v>6</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="G57" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I57">
+        <v>185</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J57">
         <v>5000</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>6003</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D58">
         <v>2</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F58">
         <v>6</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="G58" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I58">
+        <v>196</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J58">
         <v>5000</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>6004</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F59">
         <v>6</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="G59" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="I59">
+        <v>197</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J59">
         <v>5000</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>6005</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D60">
         <v>2</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F60">
         <v>6</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I60">
+        <v>198</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J60">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>6006</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F61">
         <v>6</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="I61">
+        <v>199</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="J61">
         <v>5000</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>6007</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D62">
         <v>3</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F62">
         <v>6</v>
       </c>
-      <c r="F62" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="G62" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I62">
+        <v>200</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J62">
         <v>5000</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>6008</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F63">
         <v>6</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="G63" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I63">
+        <v>201</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J63">
         <v>5000</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>6009</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F64">
         <v>6</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="G64" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="I64">
+        <v>202</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J64">
         <v>5000</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>6010</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D65">
         <v>4</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F65">
         <v>6</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="G65" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="I65">
+        <v>203</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J65">
         <v>5000</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>6011</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66">
         <v>5</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F66">
         <v>6</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="G66" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="I66">
+        <v>204</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J66">
         <v>5000</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>6020</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F67">
         <v>7</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="G67" t="s">
-        <v>229</v>
-      </c>
-      <c r="I67">
+      <c r="G67" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H67" t="s">
+        <v>227</v>
+      </c>
+      <c r="J67">
         <v>5000</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>6021</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F68">
         <v>7</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G68" t="s">
-        <v>230</v>
-      </c>
-      <c r="I68">
+      <c r="G68" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H68" t="s">
+        <v>228</v>
+      </c>
+      <c r="J68">
         <v>5000</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>6022</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D69">
         <v>3</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F69">
         <v>7</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G69" t="s">
-        <v>231</v>
-      </c>
-      <c r="I69">
+      <c r="G69" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H69" t="s">
+        <v>229</v>
+      </c>
+      <c r="J69">
         <v>5000</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>6023</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D70">
         <v>4</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F70">
         <v>7</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G70" t="s">
-        <v>232</v>
-      </c>
-      <c r="I70">
+      <c r="G70" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H70" t="s">
+        <v>230</v>
+      </c>
+      <c r="J70">
         <v>5000</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>6024</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D71">
         <v>5</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F71">
         <v>7</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G71" t="s">
-        <v>233</v>
-      </c>
-      <c r="I71">
+      <c r="G71" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" t="s">
+        <v>231</v>
+      </c>
+      <c r="J71">
         <v>5000</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>6025</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F72">
         <v>7</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="G72" t="s">
-        <v>228</v>
-      </c>
-      <c r="I72">
+      <c r="G72" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H72" t="s">
+        <v>226</v>
+      </c>
+      <c r="J72">
         <v>5000</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>6030</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73">
         <v>8</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G73" t="s">
-        <v>237</v>
-      </c>
-      <c r="I73">
+      <c r="G73" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H73" t="s">
+        <v>235</v>
+      </c>
+      <c r="J73">
         <v>5000</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>6031</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D74">
         <v>2</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F74">
         <v>8</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G74" t="s">
-        <v>238</v>
-      </c>
-      <c r="I74">
+      <c r="G74" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H74" t="s">
+        <v>236</v>
+      </c>
+      <c r="J74">
         <v>5000</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>6032</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F75">
         <v>8</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="G75" t="s">
-        <v>236</v>
-      </c>
-      <c r="I75">
+      <c r="G75" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H75" t="s">
+        <v>234</v>
+      </c>
+      <c r="J75">
         <v>5000</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>6033</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D76">
         <v>3</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F76">
         <v>8</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G76" t="s">
-        <v>239</v>
-      </c>
-      <c r="I76">
+      <c r="G76" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H76" t="s">
+        <v>237</v>
+      </c>
+      <c r="J76">
         <v>5000</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>6034</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D77">
         <v>4</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F77">
         <v>8</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G77" t="s">
-        <v>235</v>
-      </c>
-      <c r="I77">
+      <c r="G77" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H77" t="s">
+        <v>233</v>
+      </c>
+      <c r="J77">
         <v>5000</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78">
         <v>6035</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D78">
         <v>5</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F78">
         <v>8</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G78" t="s">
-        <v>234</v>
-      </c>
-      <c r="I78">
+      <c r="G78" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H78" t="s">
+        <v>232</v>
+      </c>
+      <c r="J78">
         <v>5000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80E6CE1-3024-4B0E-A5E9-C683F9C4125A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FE6D1-486C-41E9-BFC4-98212D3470EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -52,6 +53,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="277">
   <si>
     <t>##var</t>
   </si>
@@ -308,18 +310,6 @@
     <t>礼盒</t>
   </si>
   <si>
-    <t>里面包含各类初级零工所需的凭证，有较小概率获得中级零工凭证</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_gift_box]</t>
-  </si>
-  <si>
-    <t>4000,1,50;4001,1,50;4002,1,1;4003,1,50;4004,1,50;4005,1,1;4006,1,1;4008,1,50;4009,1,50;4010,1,1;4011,1,1;4013,1,50;4014,1,50;4015,1,1;4016,1,1;4018,1,50;4019,1,50;4020,1,1;4021,1,1;4023,1,10;4024,1,1</t>
-  </si>
-  <si>
-    <t>社区物资礼盒</t>
-  </si>
-  <si>
     <t>社区给居民提交材料的回馈奖励，可以获得各种物资</t>
   </si>
   <si>
@@ -834,10 +824,6 @@
   </si>
   <si>
     <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_time]</t>
-  </si>
-  <si>
-    <t>101,100,100;1010,1,100;1011,1,20;3000,1,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>初级材料礼盒</t>
@@ -852,10 +838,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_gift_box]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5000,1,100;5001,1,100;5002,1,100;5003,1,100;5004,1,100;5005,1,10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -876,6 +858,74 @@
   </si>
   <si>
     <t>替换 Base 中的 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级社区物资礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低级社区物资礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帮助社区居民获得的回馈奖励，可以获得各种物资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,100,100;1010,1,100;1011,1,10;3000,1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000,1,50;4001,1,50;4003,1,50;4004,1,50;4008,1,50;4009,1,50;4013,1,50;4014,1,50;4018,1,50;4019,1,50;4023,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级零工凭证礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里面包含各类初级零工所需的凭证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里面包含各类中级零工所需的凭证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级零工凭证礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里面包含各类高级零工所需的凭证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4002,1,50;4005,1,50;4006,1,50;4010,1,50;4011,1,50;4015,1,50;4016,1,50;4020,1,50;4021,1,50;4024,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4007,1,50;4012,1,50;4017,1,50;4022,1,50;4025,1,100,4026,1,50;4027,1,20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1218,24 +1268,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="79.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="74.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="181.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="79.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="74.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181.25" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1323,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1311,7 +1361,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1349,7 +1399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1384,10 +1434,10 @@
         <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1422,7 +1472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1457,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1492,7 +1542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1527,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1562,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1570,7 +1620,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>28</v>
@@ -1591,7 +1641,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1599,7 +1649,7 @@
         <v>51</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>28</v>
@@ -1620,7 +1670,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1649,7 +1699,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>1013</v>
       </c>
@@ -1678,7 +1728,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1050</v>
       </c>
@@ -1713,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1051</v>
       </c>
@@ -1748,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>1052</v>
       </c>
@@ -1783,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>2000</v>
       </c>
@@ -1791,7 +1841,7 @@
         <v>73</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>74</v>
@@ -1812,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>3000</v>
       </c>
@@ -1820,7 +1870,7 @@
         <v>77</v>
       </c>
       <c r="D18" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>78</v>
@@ -1829,202 +1879,214 @@
         <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>4200</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>81</v>
+        <v>6000</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>3001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="F19">
         <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>4200</v>
+        <v>6000</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="L19"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>3002</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="D20" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F20">
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>4200</v>
+        <v>6000</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>3010</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21">
-        <v>4000</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>87</v>
+      <c r="I21">
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>4000</v>
+        <v>6000</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22">
-        <v>4001</v>
+        <v>3011</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>261</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>89</v>
+        <v>263</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>90</v>
+        <v>264</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
       </c>
       <c r="J22">
+        <v>6000</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L22"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>3020</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>6000</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24">
         <v>4000</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>4002</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23">
-        <v>4000</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <v>4003</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F24">
         <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J24">
         <v>4000</v>
@@ -2033,27 +2095,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25">
-        <v>4004</v>
+        <v>4001</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="J25">
         <v>4000</v>
@@ -2062,201 +2124,201 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>4005</v>
+        <v>4002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D26" s="1">
         <v>3</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F26">
         <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26">
+        <v>4000</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>4003</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27">
+        <v>4000</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>4004</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28">
+        <v>4000</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>4005</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J29">
+        <v>3800</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>4006</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J30">
+        <v>4500</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>4007</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="J26">
-        <v>3800</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27">
-        <v>4006</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D31" s="1">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="J31">
+        <v>4500</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>4008</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J27">
-        <v>4500</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28">
-        <v>4007</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="1">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J28">
-        <v>4500</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <v>4008</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F29">
-        <v>4</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J29">
-        <v>4000</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <v>4009</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F30">
-        <v>4</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H30" t="s">
-        <v>114</v>
-      </c>
-      <c r="J30">
-        <v>4000</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31">
-        <v>4010</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" s="1">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31">
-        <v>4</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J31">
-        <v>4000</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32">
-        <v>4011</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32">
-        <v>4</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="J32">
         <v>4000</v>
@@ -2265,27 +2327,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33">
-        <v>4012</v>
+        <v>4009</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
+        <v>108</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F33">
         <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>123</v>
+        <v>109</v>
+      </c>
+      <c r="H33" t="s">
+        <v>110</v>
       </c>
       <c r="J33">
         <v>4000</v>
@@ -2294,27 +2356,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34">
-        <v>4013</v>
+        <v>4010</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
+        <v>111</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F34">
         <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="J34">
         <v>4000</v>
@@ -2323,85 +2385,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B35">
-        <v>4014</v>
+        <v>4011</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35">
+        <v>114</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J35">
+        <v>4000</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <v>4012</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36">
+        <v>4000</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37">
+        <v>4013</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37">
         <v>2</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35">
-        <v>4</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J35">
-        <v>4200</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36">
-        <v>4015</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36">
-        <v>4</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J36">
-        <v>4400</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37">
-        <v>4016</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F37">
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H37" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="J37">
         <v>4000</v>
@@ -2410,317 +2472,317 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38">
+        <v>4014</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38">
+        <v>4200</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <v>4015</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J39">
+        <v>4400</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>4016</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H40" t="s">
+        <v>131</v>
+      </c>
+      <c r="J40">
+        <v>4000</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41">
         <v>4017</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41">
+        <v>4000</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>4018</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D38">
-        <v>4</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F38">
-        <v>4</v>
-      </c>
-      <c r="G38" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="J42">
+        <v>5500</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <v>4019</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J38">
-        <v>4000</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39">
-        <v>4018</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39">
-        <v>4</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="J43">
+        <v>5500</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <v>4020</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="J39">
-        <v>5500</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40">
-        <v>4019</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D40">
-        <v>2</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40">
-        <v>4</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J40">
-        <v>5500</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41">
-        <v>4020</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41">
-        <v>4</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J41">
-        <v>4500</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42">
-        <v>4021</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42">
-        <v>3</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F42">
-        <v>4</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J42">
-        <v>4500</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43">
-        <v>4022</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43">
-        <v>4</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43">
-        <v>4</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J43">
-        <v>4500</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44">
-        <v>4023</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="D44">
         <v>3</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="J44">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45">
-        <v>4024</v>
+        <v>4021</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D45">
         <v>3</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F45">
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H45" t="s">
-        <v>159</v>
+        <v>145</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="J45">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46">
-        <v>4025</v>
+        <v>4022</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F46">
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="J46">
+        <v>4500</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B47">
+        <v>4023</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J47">
         <v>5000</v>
       </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47">
-        <v>4026</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F47">
-        <v>4</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J47">
-        <v>5200</v>
-      </c>
       <c r="L47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B48">
-        <v>4027</v>
+        <v>4024</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F48">
         <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
+      </c>
+      <c r="H48" t="s">
+        <v>155</v>
       </c>
       <c r="J48">
         <v>5500</v>
@@ -2729,27 +2791,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49">
-        <v>4028</v>
+        <v>4025</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="F49">
         <v>4</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="J49">
         <v>5000</v>
@@ -2758,143 +2820,143 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B50">
-        <v>5000</v>
+        <v>4026</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="F50">
+        <v>4</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J50">
+        <v>5200</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B51">
+        <v>4027</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51">
         <v>5</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J50">
-        <v>6000</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51">
-        <v>5001</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D51">
-        <v>3</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="J51">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B52">
-        <v>5002</v>
+        <v>4028</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H52" t="s">
-        <v>182</v>
+        <v>167</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="J52">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B53">
-        <v>5003</v>
+        <v>5000</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F53">
         <v>5</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H53" t="s">
-        <v>185</v>
+        <v>171</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="J53">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B54">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H54" t="s">
-        <v>188</v>
+        <v>174</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="J54">
         <v>6000</v>
@@ -2903,27 +2965,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B55">
-        <v>5005</v>
+        <v>5002</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>263</v>
+        <v>170</v>
       </c>
       <c r="F55">
         <v>5</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="H55" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="J55">
         <v>6000</v>
@@ -2932,143 +2994,143 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B56">
-        <v>5006</v>
+        <v>5003</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F56">
         <v>5</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H56" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="J56">
+        <v>7000</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>5004</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H57" t="s">
+        <v>184</v>
+      </c>
+      <c r="J57">
         <v>6000</v>
       </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B57">
+      <c r="L57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>5005</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H58" t="s">
+        <v>256</v>
+      </c>
+      <c r="J58">
         <v>6000</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F57">
-        <v>6</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J57">
-        <v>5000</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B58">
-        <v>6001</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F58">
-        <v>6</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="J58">
-        <v>5000</v>
-      </c>
       <c r="L58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B59">
-        <v>6002</v>
+        <v>5006</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="F59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
+      </c>
+      <c r="H59" t="s">
+        <v>187</v>
       </c>
       <c r="J59">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60">
-        <v>6003</v>
+        <v>6000</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F60">
         <v>6</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="J60">
         <v>5000</v>
@@ -3077,27 +3139,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F61">
         <v>6</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J61">
         <v>5000</v>
@@ -3106,27 +3168,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>6005</v>
+        <v>6002</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F62">
         <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="J62">
         <v>5000</v>
@@ -3135,27 +3197,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F63">
         <v>6</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="J63">
         <v>5000</v>
@@ -3164,27 +3226,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>6007</v>
+        <v>6004</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F64">
         <v>6</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="J64">
         <v>5000</v>
@@ -3193,27 +3255,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>6008</v>
+        <v>6005</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F65">
         <v>6</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="J65">
         <v>5000</v>
@@ -3222,27 +3284,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F66">
         <v>6</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="J66">
         <v>5000</v>
@@ -3251,27 +3313,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>6010</v>
+        <v>6007</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F67">
         <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="J67">
         <v>5000</v>
@@ -3280,27 +3342,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F68">
         <v>6</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J68">
         <v>5000</v>
@@ -3309,27 +3371,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>6020</v>
+        <v>6009</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="F69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H69" t="s">
-        <v>231</v>
+        <v>217</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="J69">
         <v>5000</v>
@@ -3338,27 +3400,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>6021</v>
+        <v>6010</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="H70" t="s">
-        <v>233</v>
+        <v>220</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="J70">
         <v>5000</v>
@@ -3367,27 +3429,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>6022</v>
+        <v>6011</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="F71">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="H71" t="s">
-        <v>235</v>
+        <v>223</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="J71">
         <v>5000</v>
@@ -3396,27 +3458,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>6023</v>
+        <v>6020</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F72">
         <v>7</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="H72" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="J72">
         <v>5000</v>
@@ -3425,27 +3487,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>6024</v>
+        <v>6021</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F73">
         <v>7</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="H73" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="J73">
         <v>5000</v>
@@ -3454,27 +3516,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>6025</v>
+        <v>6022</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F74">
         <v>7</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H74" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="J74">
         <v>5000</v>
@@ -3483,27 +3545,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>6030</v>
+        <v>6023</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="F75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H75" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="J75">
         <v>5000</v>
@@ -3512,27 +3574,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>6031</v>
+        <v>6024</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="H76" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="J76">
         <v>5000</v>
@@ -3541,27 +3603,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>6032</v>
+        <v>6025</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="F77">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="H77" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J77">
         <v>5000</v>
@@ -3570,27 +3632,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B78">
-        <v>6033</v>
+        <v>6030</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F78">
         <v>8</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="H78" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="J78">
         <v>5000</v>
@@ -3599,27 +3661,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>6034</v>
+        <v>6031</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F79">
         <v>8</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H79" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="J79">
         <v>5000</v>
@@ -3628,32 +3690,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>6035</v>
+        <v>6032</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F80">
         <v>8</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H80" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="J80">
         <v>5000</v>
       </c>
       <c r="L80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B81">
+        <v>6033</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F81">
+        <v>8</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H81" t="s">
+        <v>246</v>
+      </c>
+      <c r="J81">
+        <v>5000</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B82">
+        <v>6034</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F82">
+        <v>8</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" t="s">
+        <v>248</v>
+      </c>
+      <c r="J82">
+        <v>5000</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>6035</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D83">
+        <v>5</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F83">
+        <v>8</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H83" t="s">
+        <v>250</v>
+      </c>
+      <c r="J83">
+        <v>5000</v>
+      </c>
+      <c r="L83">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3FE6D1-486C-41E9-BFC4-98212D3470EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419DE88A-66E4-4409-B4E7-3A0F78D6E650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419DE88A-66E4-4409-B4E7-3A0F78D6E650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428C9E2-C8E3-4F22-BB4D-ACEC2732AB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2901,7 +2901,7 @@
         <v>168</v>
       </c>
       <c r="J52">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="L52">
         <v>0</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428C9E2-C8E3-4F22-BB4D-ACEC2732AB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797CB966-722F-4A83-B40A-5E6B176FBE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -838,10 +838,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5000,1,100;5001,1,100;5002,1,100;5003,1,100;5004,1,100;5005,1,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>小鱼干</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -885,18 +881,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>101,100,100;1010,1,100;1011,1,10;3000,1,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4000,1,50;4001,1,50;4003,1,50;4004,1,50;4008,1,50;4009,1,50;4013,1,50;4014,1,50;4018,1,50;4019,1,50;4023,1,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>中级零工凭证礼盒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -921,11 +905,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4002,1,50;4005,1,50;4006,1,50;4010,1,50;4011,1,50;4015,1,50;4016,1,50;4020,1,50;4021,1,50;4024,1,100</t>
+    <t>4007,1,50;4012,1,50;4017,1,50;4022,1,50;4025,1,100,4026,1,50;4027,1,20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4007,1,50;4012,1,50;4017,1,50;4022,1,50;4025,1,100,4026,1,50;4027,1,20</t>
+    <t>5000,1,100;5001,1,100;5002,1,100;5003,1,100;5004,1,100;5005,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3001,1,10;4000,1,50;4001,1,50;4003,1,50;4004,1,50;4008,1,50;4009,1,50;4013,1,50;4014,1,50;4018,1,50;4019,1,50;4023,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002,1,10;4002,1,50;4005,1,50;4006,1,50;4010,1,50;4011,1,50;4015,1,50;4016,1,50;4020,1,50;4021,1,50;4024,1,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3011,1,10;101,100,100;1010,1,100;1011,1,10;3000,1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1434,7 +1434,7 @@
         <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1879,10 +1879,10 @@
         <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -1891,7 +1891,7 @@
         <v>6000</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>3001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -1914,10 +1914,10 @@
         <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>6000</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L19"/>
     </row>
@@ -1935,7 +1935,7 @@
         <v>3002</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -1947,10 +1947,10 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>6000</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L20"/>
     </row>
@@ -1968,7 +1968,7 @@
         <v>3010</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -1983,7 +1983,7 @@
         <v>79</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         <v>6000</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>3011</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -2015,10 +2015,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="L22"/>
     </row>
@@ -2051,7 +2051,7 @@
         <v>253</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -2060,7 +2060,7 @@
         <v>6000</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>5005</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J58">
         <v>6000</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797CB966-722F-4A83-B40A-5E6B176FBE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44E17A4-0B5C-451B-9CCF-3AA09CC65C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="284">
   <si>
     <t>##var</t>
   </si>
@@ -927,6 +927,32 @@
   <si>
     <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草莓小熊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女儿一直想要的草莓小熊，为什么会从河里钓起来？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_pink_bear_plush_icon]</t>
+  </si>
+  <si>
+    <t>海洋之心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完美的吊坠，送给喵夫人最为合适了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" style="4" bestFit="1" customWidth="1"/>
@@ -3112,28 +3138,28 @@
     </row>
     <row r="60" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B60">
+        <v>5100</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H60" t="s">
+        <v>280</v>
+      </c>
+      <c r="J60">
         <v>6000</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F60">
-        <v>6</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J60">
-        <v>5000</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -3141,28 +3167,28 @@
     </row>
     <row r="61" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>6001</v>
+        <v>5101</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>189</v>
+        <v>278</v>
       </c>
       <c r="F61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>194</v>
+        <v>282</v>
+      </c>
+      <c r="H61" t="s">
+        <v>283</v>
       </c>
       <c r="J61">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -3170,10 +3196,10 @@
     </row>
     <row r="62" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B62">
-        <v>6002</v>
+        <v>6000</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3185,10 +3211,10 @@
         <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J62">
         <v>5000</v>
@@ -3199,13 +3225,13 @@
     </row>
     <row r="63" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B63">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>189</v>
@@ -3214,10 +3240,10 @@
         <v>6</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="J63">
         <v>5000</v>
@@ -3228,13 +3254,13 @@
     </row>
     <row r="64" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B64">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>189</v>
@@ -3243,10 +3269,10 @@
         <v>6</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="J64">
         <v>5000</v>
@@ -3257,10 +3283,10 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3272,10 +3298,10 @@
         <v>6</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J65">
         <v>5000</v>
@@ -3286,13 +3312,13 @@
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>189</v>
@@ -3301,10 +3327,10 @@
         <v>6</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J66">
         <v>5000</v>
@@ -3315,13 +3341,13 @@
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>189</v>
@@ -3330,10 +3356,10 @@
         <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="J67">
         <v>5000</v>
@@ -3344,10 +3370,10 @@
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -3359,10 +3385,10 @@
         <v>6</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J68">
         <v>5000</v>
@@ -3373,13 +3399,13 @@
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69">
-        <v>6009</v>
+        <v>6007</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>189</v>
@@ -3388,10 +3414,10 @@
         <v>6</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J69">
         <v>5000</v>
@@ -3402,13 +3428,13 @@
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70">
-        <v>6010</v>
+        <v>6008</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>189</v>
@@ -3417,10 +3443,10 @@
         <v>6</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J70">
         <v>5000</v>
@@ -3431,13 +3457,13 @@
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>189</v>
@@ -3446,10 +3472,10 @@
         <v>6</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J71">
         <v>5000</v>
@@ -3460,25 +3486,25 @@
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B72">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H72" t="s">
-        <v>227</v>
+        <v>220</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="J72">
         <v>5000</v>
@@ -3489,25 +3515,25 @@
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B73">
-        <v>6021</v>
+        <v>6011</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="F73">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H73" t="s">
-        <v>229</v>
+        <v>223</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="J73">
         <v>5000</v>
@@ -3518,13 +3544,13 @@
     </row>
     <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B74">
-        <v>6022</v>
+        <v>6020</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>226</v>
@@ -3533,10 +3559,10 @@
         <v>7</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H74" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J74">
         <v>5000</v>
@@ -3547,13 +3573,13 @@
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B75">
-        <v>6023</v>
+        <v>6021</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>226</v>
@@ -3562,10 +3588,10 @@
         <v>7</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H75" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J75">
         <v>5000</v>
@@ -3576,13 +3602,13 @@
     </row>
     <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B76">
-        <v>6024</v>
+        <v>6022</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>226</v>
@@ -3591,10 +3617,10 @@
         <v>7</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H76" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J76">
         <v>5000</v>
@@ -3605,13 +3631,13 @@
     </row>
     <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B77">
-        <v>6025</v>
+        <v>6023</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>226</v>
@@ -3620,10 +3646,10 @@
         <v>7</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H77" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J77">
         <v>5000</v>
@@ -3634,25 +3660,25 @@
     </row>
     <row r="78" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B78">
-        <v>6030</v>
+        <v>6024</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H78" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J78">
         <v>5000</v>
@@ -3663,25 +3689,25 @@
     </row>
     <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79">
-        <v>6031</v>
+        <v>6025</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="F79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H79" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J79">
         <v>5000</v>
@@ -3692,13 +3718,13 @@
     </row>
     <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B80">
-        <v>6032</v>
+        <v>6030</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>239</v>
@@ -3707,10 +3733,10 @@
         <v>8</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H80" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J80">
         <v>5000</v>
@@ -3721,13 +3747,13 @@
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B81">
-        <v>6033</v>
+        <v>6031</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>239</v>
@@ -3736,10 +3762,10 @@
         <v>8</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H81" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J81">
         <v>5000</v>
@@ -3750,13 +3776,13 @@
     </row>
     <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82">
-        <v>6034</v>
+        <v>6032</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>239</v>
@@ -3765,10 +3791,10 @@
         <v>8</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H82" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J82">
         <v>5000</v>
@@ -3779,13 +3805,13 @@
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B83">
-        <v>6035</v>
+        <v>6033</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>239</v>
@@ -3794,15 +3820,73 @@
         <v>8</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H83" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J83">
         <v>5000</v>
       </c>
       <c r="L83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B84">
+        <v>6034</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F84">
+        <v>8</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H84" t="s">
+        <v>248</v>
+      </c>
+      <c r="J84">
+        <v>5000</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B85">
+        <v>6035</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F85">
+        <v>8</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H85" t="s">
+        <v>250</v>
+      </c>
+      <c r="J85">
+        <v>5000</v>
+      </c>
+      <c r="L85">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3E2147-3696-4CEF-82E2-5E1B785E01EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBF4E50-0F95-4249-B788-C5DC63073F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,6 +83,9 @@
     <t>level</t>
   </si>
   <si>
+    <t>inventoryType</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
     <t>replace</t>
   </si>
   <si>
-    <t>inventoryType</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -134,6 +134,9 @@
     <t>品质</t>
   </si>
   <si>
+    <t>背包类型：0不显示，1普通背包，2钓鱼背包</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -156,9 +159,6 @@
   </si>
   <si>
     <t>替换 Base 中的 ID</t>
-  </si>
-  <si>
-    <t>背包类型：0不显示，1普通背包，2钓鱼背包</t>
   </si>
   <si>
     <t>一枚模拟币</t>
@@ -948,17 +948,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -989,13 +988,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1281,7 +1280,7 @@
     <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="5" max="5" width="11" style="4" customWidth="1"/>
     <col min="6" max="6" width="9.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="12.375" style="4" customWidth="1"/>
     <col min="8" max="8" width="79.75" style="4" bestFit="1" customWidth="1"/>
@@ -1306,31 +1305,31 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -1429,31 +1428,31 @@
         <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -3785,7 +3784,7 @@
         <v>6020</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3800,10 +3799,10 @@
         <v>7</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I75" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="K75">
         <v>5000</v>
@@ -3817,10 +3816,10 @@
         <v>6021</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3832,10 +3831,10 @@
         <v>7</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I76" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K76">
         <v>5000</v>
@@ -3849,10 +3848,10 @@
         <v>6022</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3864,10 +3863,10 @@
         <v>7</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I77" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K77">
         <v>5000</v>
@@ -3881,10 +3880,10 @@
         <v>6023</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3896,10 +3895,10 @@
         <v>7</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I78" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K78">
         <v>5000</v>
@@ -3913,10 +3912,10 @@
         <v>6024</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3928,10 +3927,10 @@
         <v>7</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I79" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="K79">
         <v>5000</v>
@@ -3945,10 +3944,10 @@
         <v>6025</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3960,10 +3959,10 @@
         <v>7</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I80" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K80">
         <v>5000</v>
@@ -4165,7 +4164,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBF4E50-0F95-4249-B788-C5DC63073F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D142DA32-0B86-45F9-94B6-FD173335B95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="292">
   <si>
     <t>##var</t>
   </si>
@@ -731,9 +731,6 @@
     <t>稀有材料</t>
   </si>
   <si>
-    <t>女儿一直想要的草莓小熊，为什么会从河里钓起来？</t>
-  </si>
-  <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_pink_bear_plush_icon]</t>
   </si>
   <si>
@@ -933,6 +930,26 @@
   </si>
   <si>
     <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_time]</t>
+  </si>
+  <si>
+    <t>强力胶带</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务道具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>女儿一直想要的草莓小熊，为什么会从河里钓起来?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊大山需要的强力胶带，快交给他吧!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1273,25 +1290,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M87"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="79.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="181.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="79.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="181.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1373,7 +1390,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1414,7 +1431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1455,7 +1472,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1493,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1531,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1569,7 +1586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1607,7 +1624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1645,7 +1662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1677,7 +1694,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1709,7 +1726,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1741,7 +1758,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1013</v>
       </c>
@@ -1773,7 +1790,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1050</v>
       </c>
@@ -1811,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1051</v>
       </c>
@@ -1849,7 +1866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1052</v>
       </c>
@@ -1887,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2000</v>
       </c>
@@ -1919,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3000</v>
       </c>
@@ -1957,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>3001</v>
       </c>
@@ -1993,7 +2010,7 @@
       </c>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>3002</v>
       </c>
@@ -2029,7 +2046,7 @@
       </c>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>3010</v>
       </c>
@@ -2067,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>3011</v>
       </c>
@@ -2103,7 +2120,7 @@
       </c>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>3020</v>
       </c>
@@ -2141,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>3030</v>
       </c>
@@ -2179,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>4000</v>
       </c>
@@ -2211,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>4001</v>
       </c>
@@ -2243,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>4002</v>
       </c>
@@ -2275,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>4003</v>
       </c>
@@ -2307,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>4004</v>
       </c>
@@ -2339,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>4005</v>
       </c>
@@ -2371,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>4006</v>
       </c>
@@ -2403,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>4007</v>
       </c>
@@ -2435,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>4008</v>
       </c>
@@ -2467,7 +2484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>4009</v>
       </c>
@@ -2499,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>4010</v>
       </c>
@@ -2531,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>4011</v>
       </c>
@@ -2563,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>4012</v>
       </c>
@@ -2595,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>4013</v>
       </c>
@@ -2627,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>4014</v>
       </c>
@@ -2659,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>4015</v>
       </c>
@@ -2691,7 +2708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>4016</v>
       </c>
@@ -2723,7 +2740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>4017</v>
       </c>
@@ -2755,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>4018</v>
       </c>
@@ -2787,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>4019</v>
       </c>
@@ -2819,7 +2836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>4020</v>
       </c>
@@ -2851,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>4021</v>
       </c>
@@ -2883,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>4022</v>
       </c>
@@ -2915,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>4023</v>
       </c>
@@ -2947,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>4024</v>
       </c>
@@ -2979,7 +2996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>4025</v>
       </c>
@@ -3011,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>4026</v>
       </c>
@@ -3043,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>4027</v>
       </c>
@@ -3075,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>4028</v>
       </c>
@@ -3107,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>5000</v>
       </c>
@@ -3139,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>5001</v>
       </c>
@@ -3171,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>5002</v>
       </c>
@@ -3203,7 +3220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>5003</v>
       </c>
@@ -3235,7 +3252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>5004</v>
       </c>
@@ -3267,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>5005</v>
       </c>
@@ -3299,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>5006</v>
       </c>
@@ -3331,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>5100</v>
       </c>
@@ -3351,10 +3368,10 @@
         <v>5</v>
       </c>
       <c r="H61" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I61" t="s">
         <v>220</v>
-      </c>
-      <c r="I61" t="s">
-        <v>221</v>
       </c>
       <c r="K61">
         <v>6000</v>
@@ -3363,12 +3380,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>5101</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -3383,10 +3400,10 @@
         <v>5</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="I62" t="s">
-        <v>224</v>
+        <v>222</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="K62">
         <v>6000</v>
@@ -3395,44 +3412,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63">
+        <v>5102</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" s="1">
+        <v>5</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I63" t="s">
+        <v>223</v>
+      </c>
+      <c r="K63">
         <v>6000</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G63">
-        <v>6</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K63">
-        <v>5000</v>
-      </c>
       <c r="M63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3441,16 +3458,16 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G64">
         <v>6</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K64">
         <v>5000</v>
@@ -3459,12 +3476,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3473,16 +3490,16 @@
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G65">
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K65">
         <v>5000</v>
@@ -3491,30 +3508,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G66">
         <v>6</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K66">
         <v>5000</v>
@@ -3523,12 +3540,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3537,16 +3554,16 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G67">
         <v>6</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K67">
         <v>5000</v>
@@ -3555,12 +3572,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3569,16 +3586,16 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G68">
         <v>6</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K68">
         <v>5000</v>
@@ -3587,30 +3604,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G69">
         <v>6</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="K69">
         <v>5000</v>
@@ -3619,12 +3636,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3633,16 +3650,16 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G70">
         <v>6</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K70">
         <v>5000</v>
@@ -3651,12 +3668,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3665,16 +3682,16 @@
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K71">
         <v>5000</v>
@@ -3683,30 +3700,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G72">
         <v>6</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="K72">
         <v>5000</v>
@@ -3715,12 +3732,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -3729,16 +3746,16 @@
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G73">
         <v>6</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K73">
         <v>5000</v>
@@ -3747,30 +3764,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G74">
         <v>6</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="K74">
         <v>5000</v>
@@ -3779,30 +3796,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="G75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I75" t="s">
-        <v>274</v>
+        <v>259</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="K75">
         <v>5000</v>
@@ -3811,30 +3828,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="G76">
         <v>7</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I76" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="K76">
         <v>5000</v>
@@ -3843,30 +3860,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G77">
         <v>7</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="I77" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K77">
         <v>5000</v>
@@ -3875,30 +3892,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G78">
         <v>7</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I78" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K78">
         <v>5000</v>
@@ -3907,30 +3924,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B79">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G79">
         <v>7</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I79" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K79">
         <v>5000</v>
@@ -3939,30 +3956,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G80">
         <v>7</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I80" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="K80">
         <v>5000</v>
@@ -3971,30 +3988,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>6030</v>
+        <v>6025</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="G81">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I81" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="K81">
         <v>5000</v>
@@ -4003,30 +4020,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I82" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K82">
         <v>5000</v>
@@ -4035,12 +4052,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4049,16 +4066,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I83" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K83">
         <v>5000</v>
@@ -4067,30 +4084,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="I84" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K84">
         <v>5000</v>
@@ -4099,30 +4116,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I85" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K85">
         <v>5000</v>
@@ -4131,35 +4148,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I86" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K86">
         <v>5000</v>
       </c>
       <c r="M86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B87">
+        <v>6035</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D87">
+        <v>5</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I87" t="s">
+        <v>286</v>
+      </c>
+      <c r="K87">
+        <v>5000</v>
+      </c>
+      <c r="M87">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D142DA32-0B86-45F9-94B6-FD173335B95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B316162E-F470-4BDD-9660-E05C8C97C7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="564" windowWidth="30696" windowHeight="15996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -52,6 +53,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="等线"/>
+            <family val="3"/>
             <charset val="134"/>
             <scheme val="minor"/>
           </rPr>
@@ -740,9 +742,6 @@
     <t>完美的吊坠，送给喵夫人最为合适了</t>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
-  </si>
-  <si>
     <t>小白条</t>
   </si>
   <si>
@@ -949,6 +948,10 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[dream_city_strong_duct_tape_icon]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -975,6 +978,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1291,24 +1295,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M87"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="79.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="181.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="79.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="181.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1353,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1390,7 +1394,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1431,7 +1435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1510,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1548,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1586,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1624,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1662,7 +1666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1694,7 +1698,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1726,7 +1730,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1758,7 +1762,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>1013</v>
       </c>
@@ -1790,7 +1794,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1050</v>
       </c>
@@ -1828,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1051</v>
       </c>
@@ -1866,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>1052</v>
       </c>
@@ -1904,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>2000</v>
       </c>
@@ -1936,7 +1940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>3000</v>
       </c>
@@ -1974,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>3001</v>
       </c>
@@ -2010,7 +2014,7 @@
       </c>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>3002</v>
       </c>
@@ -2046,7 +2050,7 @@
       </c>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>3010</v>
       </c>
@@ -2084,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>3011</v>
       </c>
@@ -2120,7 +2124,7 @@
       </c>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>3020</v>
       </c>
@@ -2158,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>3030</v>
       </c>
@@ -2196,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>4000</v>
       </c>
@@ -2228,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>4001</v>
       </c>
@@ -2260,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>4002</v>
       </c>
@@ -2292,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>4003</v>
       </c>
@@ -2324,7 +2328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>4004</v>
       </c>
@@ -2356,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>4005</v>
       </c>
@@ -2388,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>4006</v>
       </c>
@@ -2420,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>4007</v>
       </c>
@@ -2452,7 +2456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>4008</v>
       </c>
@@ -2484,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>4009</v>
       </c>
@@ -2516,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>4010</v>
       </c>
@@ -2548,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>4011</v>
       </c>
@@ -2580,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>4012</v>
       </c>
@@ -2612,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>4013</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>4014</v>
       </c>
@@ -2676,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>4015</v>
       </c>
@@ -2708,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>4016</v>
       </c>
@@ -2740,7 +2744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>4017</v>
       </c>
@@ -2772,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>4018</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>4019</v>
       </c>
@@ -2836,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>4020</v>
       </c>
@@ -2868,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>4021</v>
       </c>
@@ -2900,7 +2904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>4022</v>
       </c>
@@ -2932,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>4023</v>
       </c>
@@ -2964,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49">
         <v>4024</v>
       </c>
@@ -2996,7 +3000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>4025</v>
       </c>
@@ -3028,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>4026</v>
       </c>
@@ -3060,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>4027</v>
       </c>
@@ -3092,7 +3096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>4028</v>
       </c>
@@ -3124,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>5000</v>
       </c>
@@ -3156,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>5001</v>
       </c>
@@ -3188,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>5002</v>
       </c>
@@ -3220,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>5003</v>
       </c>
@@ -3252,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>5004</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>5005</v>
       </c>
@@ -3316,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>5006</v>
       </c>
@@ -3348,7 +3352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>5100</v>
       </c>
@@ -3368,7 +3372,7 @@
         <v>5</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I61" t="s">
         <v>220</v>
@@ -3380,7 +3384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>5101</v>
       </c>
@@ -3403,7 +3407,7 @@
         <v>222</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K62">
         <v>6000</v>
@@ -3412,30 +3416,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B63">
         <v>5102</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="D63">
-        <v>5</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="G63" s="1">
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I63" t="s">
-        <v>223</v>
+        <v>289</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="K63">
         <v>6000</v>
@@ -3444,12 +3448,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>6000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3458,16 +3462,16 @@
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G64">
         <v>6</v>
       </c>
       <c r="H64" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="K64">
         <v>5000</v>
@@ -3476,12 +3480,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>6001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3490,16 +3494,16 @@
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G65">
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="K65">
         <v>5000</v>
@@ -3508,12 +3512,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>6002</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3522,16 +3526,16 @@
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G66">
         <v>6</v>
       </c>
       <c r="H66" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="K66">
         <v>5000</v>
@@ -3540,12 +3544,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>6003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3554,16 +3558,16 @@
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G67">
         <v>6</v>
       </c>
       <c r="H67" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="K67">
         <v>5000</v>
@@ -3572,12 +3576,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>6004</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3586,16 +3590,16 @@
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G68">
         <v>6</v>
       </c>
       <c r="H68" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="K68">
         <v>5000</v>
@@ -3604,12 +3608,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>6005</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3618,16 +3622,16 @@
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G69">
         <v>6</v>
       </c>
       <c r="H69" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="K69">
         <v>5000</v>
@@ -3636,12 +3640,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B70">
         <v>6006</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -3650,16 +3654,16 @@
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G70">
         <v>6</v>
       </c>
       <c r="H70" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="K70">
         <v>5000</v>
@@ -3668,12 +3672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>6007</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3682,16 +3686,16 @@
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="K71">
         <v>5000</v>
@@ -3700,12 +3704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>6008</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -3714,16 +3718,16 @@
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G72">
         <v>6</v>
       </c>
       <c r="H72" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="K72">
         <v>5000</v>
@@ -3732,12 +3736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>6009</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -3746,16 +3750,16 @@
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G73">
         <v>6</v>
       </c>
       <c r="H73" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="K73">
         <v>5000</v>
@@ -3764,12 +3768,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>6010</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -3778,16 +3782,16 @@
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G74">
         <v>6</v>
       </c>
       <c r="H74" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="K74">
         <v>5000</v>
@@ -3796,12 +3800,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B75">
         <v>6011</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D75">
         <v>5</v>
@@ -3810,16 +3814,16 @@
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G75">
         <v>6</v>
       </c>
       <c r="H75" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="K75">
         <v>5000</v>
@@ -3828,12 +3832,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B76">
         <v>6020</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3842,16 +3846,16 @@
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G76">
         <v>7</v>
       </c>
       <c r="H76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I76" t="s">
         <v>272</v>
-      </c>
-      <c r="I76" t="s">
-        <v>273</v>
       </c>
       <c r="K76">
         <v>5000</v>
@@ -3860,30 +3864,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B77">
         <v>6021</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="G77">
         <v>7</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I77" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K77">
         <v>5000</v>
@@ -3892,12 +3896,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B78">
         <v>6022</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3906,16 +3910,16 @@
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G78">
         <v>7</v>
       </c>
       <c r="H78" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I78" t="s">
         <v>264</v>
-      </c>
-      <c r="I78" t="s">
-        <v>265</v>
       </c>
       <c r="K78">
         <v>5000</v>
@@ -3924,12 +3928,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79">
         <v>6023</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -3938,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G79">
         <v>7</v>
       </c>
       <c r="H79" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I79" t="s">
         <v>266</v>
-      </c>
-      <c r="I79" t="s">
-        <v>267</v>
       </c>
       <c r="K79">
         <v>5000</v>
@@ -3956,12 +3960,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B80">
         <v>6024</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -3970,16 +3974,16 @@
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G80">
         <v>7</v>
       </c>
       <c r="H80" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I80" t="s">
         <v>268</v>
-      </c>
-      <c r="I80" t="s">
-        <v>269</v>
       </c>
       <c r="K80">
         <v>5000</v>
@@ -3988,12 +3992,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B81">
         <v>6025</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D81">
         <v>5</v>
@@ -4002,16 +4006,16 @@
         <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G81">
         <v>7</v>
       </c>
       <c r="H81" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I81" t="s">
         <v>270</v>
-      </c>
-      <c r="I81" t="s">
-        <v>271</v>
       </c>
       <c r="K81">
         <v>5000</v>
@@ -4020,30 +4024,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>6030</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="G82">
         <v>8</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K82">
         <v>5000</v>
@@ -4052,12 +4056,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B83">
         <v>6031</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4066,16 +4070,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G83">
         <v>8</v>
       </c>
       <c r="H83" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I83" t="s">
         <v>277</v>
-      </c>
-      <c r="I83" t="s">
-        <v>278</v>
       </c>
       <c r="K83">
         <v>5000</v>
@@ -4084,12 +4088,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B84">
         <v>6032</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4098,16 +4102,16 @@
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G84">
         <v>8</v>
       </c>
       <c r="H84" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="I84" t="s">
         <v>279</v>
-      </c>
-      <c r="I84" t="s">
-        <v>280</v>
       </c>
       <c r="K84">
         <v>5000</v>
@@ -4116,12 +4120,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B85">
         <v>6033</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -4130,16 +4134,16 @@
         <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G85">
         <v>8</v>
       </c>
       <c r="H85" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I85" t="s">
         <v>281</v>
-      </c>
-      <c r="I85" t="s">
-        <v>282</v>
       </c>
       <c r="K85">
         <v>5000</v>
@@ -4148,12 +4152,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B86">
         <v>6034</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4162,16 +4166,16 @@
         <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G86">
         <v>8</v>
       </c>
       <c r="H86" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I86" t="s">
         <v>283</v>
-      </c>
-      <c r="I86" t="s">
-        <v>284</v>
       </c>
       <c r="K86">
         <v>5000</v>
@@ -4180,12 +4184,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B87">
         <v>6035</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D87">
         <v>5</v>
@@ -4194,16 +4198,16 @@
         <v>0</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G87">
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I87" t="s">
         <v>285</v>
-      </c>
-      <c r="I87" t="s">
-        <v>286</v>
       </c>
       <c r="K87">
         <v>5000</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B316162E-F470-4BDD-9660-E05C8C97C7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC1CA1-8962-47AA-BB1A-9B0AD9E467EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="297">
   <si>
     <t>##var</t>
   </si>
@@ -952,6 +952,24 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[dream_city_strong_duct_tape_icon]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级社区物资礼盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>为社区贡献卓越力量后获得的最高回馈，可以获得更丰富的物资</t>
+  </si>
+  <si>
+    <t>3001,1,55;3002,1,25;101,888,100;101,1288,100;101,1888,50;1010,3,100;1011,2,80</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_3]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_2]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1294,25 +1312,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M87"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M88"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="79.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="74.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="181.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="79.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="74.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="181.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1371,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1394,7 +1412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1435,7 +1453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1476,7 +1494,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1514,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1590,7 +1608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1666,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1698,7 +1716,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1730,7 +1748,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1762,7 +1780,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1013</v>
       </c>
@@ -1794,7 +1812,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1050</v>
       </c>
@@ -1832,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1051</v>
       </c>
@@ -1870,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1052</v>
       </c>
@@ -1908,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2000</v>
       </c>
@@ -1940,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3000</v>
       </c>
@@ -1978,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>3001</v>
       </c>
@@ -2014,7 +2032,7 @@
       </c>
       <c r="M19"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>3002</v>
       </c>
@@ -2050,7 +2068,7 @@
       </c>
       <c r="M20"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>3010</v>
       </c>
@@ -2088,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>3011</v>
       </c>
@@ -2111,7 +2129,7 @@
         <v>98</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2124,15 +2142,15 @@
       </c>
       <c r="M22"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23">
-        <v>3020</v>
+        <v>3012</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>100</v>
+        <v>292</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2144,10 +2162,10 @@
         <v>3</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2156,18 +2174,18 @@
         <v>6000</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>102</v>
+        <v>294</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -2182,10 +2200,10 @@
         <v>3</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2194,50 +2212,56 @@
         <v>6000</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>3030</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>6000</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B25">
+      <c r="M25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>4000</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25">
-        <v>4</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25">
-        <v>4000</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>4001</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -2252,10 +2276,10 @@
         <v>4</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K26">
         <v>4000</v>
@@ -2264,15 +2288,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2284,10 +2308,10 @@
         <v>4</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K27">
         <v>4000</v>
@@ -2296,15 +2320,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2316,10 +2340,10 @@
         <v>4</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K28">
         <v>4000</v>
@@ -2328,12 +2352,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -2348,10 +2372,10 @@
         <v>4</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K29">
         <v>4000</v>
@@ -2360,15 +2384,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2380,24 +2404,24 @@
         <v>4</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I30" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="K30">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -2412,27 +2436,27 @@
         <v>4</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="I31" t="s">
+        <v>125</v>
       </c>
       <c r="K31">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D32" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2444,10 +2468,10 @@
         <v>4</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K32">
         <v>4500</v>
@@ -2456,15 +2480,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D33" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2476,24 +2500,24 @@
         <v>4</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K33">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
@@ -2508,10 +2532,10 @@
         <v>4</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="K34">
         <v>4000</v>
@@ -2520,15 +2544,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D35" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2540,10 +2564,10 @@
         <v>4</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
+      </c>
+      <c r="I35" t="s">
+        <v>137</v>
       </c>
       <c r="K35">
         <v>4000</v>
@@ -2552,12 +2576,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -2572,10 +2596,10 @@
         <v>4</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K36">
         <v>4000</v>
@@ -2584,15 +2608,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
+        <v>141</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2604,10 +2628,10 @@
         <v>4</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K37">
         <v>4000</v>
@@ -2616,15 +2640,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -2636,10 +2660,10 @@
         <v>4</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K38">
         <v>4000</v>
@@ -2648,12 +2672,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2668,27 +2692,27 @@
         <v>4</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K39">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2700,24 +2724,24 @@
         <v>4</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K40">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="M40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2732,27 +2756,27 @@
         <v>4</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I41" t="s">
-        <v>158</v>
+        <v>154</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="K41">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="M41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2764,10 +2788,10 @@
         <v>4</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
+      </c>
+      <c r="I42" t="s">
+        <v>158</v>
       </c>
       <c r="K42">
         <v>4000</v>
@@ -2776,15 +2800,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -2796,24 +2820,24 @@
         <v>4</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K43">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -2828,10 +2852,10 @@
         <v>4</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K44">
         <v>5500</v>
@@ -2840,15 +2864,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -2860,24 +2884,24 @@
         <v>4</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K45">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="M45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2892,10 +2916,10 @@
         <v>4</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K46">
         <v>4500</v>
@@ -2904,15 +2928,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -2924,10 +2948,10 @@
         <v>4</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K47">
         <v>4500</v>
@@ -2936,15 +2960,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -2956,27 +2980,27 @@
         <v>4</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K48">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="M48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -2988,27 +3012,27 @@
         <v>4</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I49" t="s">
-        <v>182</v>
+        <v>178</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="K49">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="M49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -3020,24 +3044,24 @@
         <v>4</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="I50" t="s">
+        <v>182</v>
       </c>
       <c r="K50">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -3052,27 +3076,27 @@
         <v>4</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K51">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="M51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3084,88 +3108,88 @@
         <v>4</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K52">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="M52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="G53">
         <v>4</v>
       </c>
       <c r="H53" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K53">
+        <v>5500</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>4028</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K53">
+      <c r="K54">
         <v>3200</v>
       </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B54">
+      <c r="M54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B55">
         <v>5000</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G54">
-        <v>5</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K54">
-        <v>6000</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B55">
-        <v>5001</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3180,10 +3204,10 @@
         <v>5</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K55">
         <v>6000</v>
@@ -3192,12 +3216,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3212,10 +3236,10 @@
         <v>5</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I56" t="s">
-        <v>205</v>
+        <v>201</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="K56">
         <v>6000</v>
@@ -3224,12 +3248,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3244,24 +3268,24 @@
         <v>5</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I57" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K57">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58">
-        <v>5004</v>
+        <v>5003</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3276,24 +3300,24 @@
         <v>5</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I58" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K58">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="M58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>5005</v>
+        <v>5004</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3308,10 +3332,10 @@
         <v>5</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I59" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K59">
         <v>6000</v>
@@ -3320,15 +3344,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>5006</v>
+        <v>5005</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3340,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I60" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K60">
         <v>6000</v>
@@ -3352,30 +3376,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>5100</v>
+        <v>5006</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="G61">
         <v>5</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
       <c r="I61" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K61">
         <v>6000</v>
@@ -3384,12 +3408,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>5101</v>
+        <v>5100</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -3404,10 +3428,10 @@
         <v>5</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+      <c r="I62" t="s">
+        <v>220</v>
       </c>
       <c r="K62">
         <v>6000</v>
@@ -3416,30 +3440,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>286</v>
+        <v>221</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G63" s="1">
+        <v>219</v>
+      </c>
+      <c r="G63">
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K63">
         <v>6000</v>
@@ -3448,44 +3472,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64">
+        <v>5102</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G64" s="1">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="K64">
         <v>6000</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="M64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>6000</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G64">
-        <v>6</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="K64">
-        <v>5000</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B65">
-        <v>6001</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3500,10 +3524,10 @@
         <v>6</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K65">
         <v>5000</v>
@@ -3512,12 +3536,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3532,10 +3556,10 @@
         <v>6</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K66">
         <v>5000</v>
@@ -3544,15 +3568,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>2</v>
@@ -3564,10 +3588,10 @@
         <v>6</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K67">
         <v>5000</v>
@@ -3576,12 +3600,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3596,10 +3620,10 @@
         <v>6</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K68">
         <v>5000</v>
@@ -3608,12 +3632,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3628,10 +3652,10 @@
         <v>6</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K69">
         <v>5000</v>
@@ -3640,15 +3664,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -3660,10 +3684,10 @@
         <v>6</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K70">
         <v>5000</v>
@@ -3672,12 +3696,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>6007</v>
+        <v>6006</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3692,10 +3716,10 @@
         <v>6</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="K71">
         <v>5000</v>
@@ -3704,12 +3728,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>6008</v>
+        <v>6007</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -3724,10 +3748,10 @@
         <v>6</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K72">
         <v>5000</v>
@@ -3736,15 +3760,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73">
         <v>2</v>
@@ -3756,10 +3780,10 @@
         <v>6</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K73">
         <v>5000</v>
@@ -3768,12 +3792,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>6010</v>
+        <v>6009</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D74">
         <v>4</v>
@@ -3788,10 +3812,10 @@
         <v>6</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K74">
         <v>5000</v>
@@ -3800,15 +3824,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E75">
         <v>2</v>
@@ -3820,10 +3844,10 @@
         <v>6</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K75">
         <v>5000</v>
@@ -3832,30 +3856,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="G76">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I76" t="s">
-        <v>272</v>
+        <v>258</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="K76">
         <v>5000</v>
@@ -3864,12 +3888,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>6021</v>
+        <v>6020</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3884,10 +3908,10 @@
         <v>7</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I77" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="K77">
         <v>5000</v>
@@ -3896,15 +3920,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>6022</v>
+        <v>6021</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3916,10 +3940,10 @@
         <v>7</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I78" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K78">
         <v>5000</v>
@@ -3928,15 +3952,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B79">
-        <v>6023</v>
+        <v>6022</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3948,10 +3972,10 @@
         <v>7</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I79" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K79">
         <v>5000</v>
@@ -3960,15 +3984,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>6024</v>
+        <v>6023</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3980,10 +4004,10 @@
         <v>7</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I80" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="K80">
         <v>5000</v>
@@ -3992,15 +4016,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>6025</v>
+        <v>6024</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4012,10 +4036,10 @@
         <v>7</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I81" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K81">
         <v>5000</v>
@@ -4024,30 +4048,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82">
-        <v>6030</v>
+        <v>6025</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="G82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I82" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="K82">
         <v>5000</v>
@@ -4056,15 +4080,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>6031</v>
+        <v>6030</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4076,10 +4100,10 @@
         <v>8</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I83" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K83">
         <v>5000</v>
@@ -4088,12 +4112,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4108,10 +4132,10 @@
         <v>8</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I84" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K84">
         <v>5000</v>
@@ -4120,15 +4144,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>6033</v>
+        <v>6032</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4140,10 +4164,10 @@
         <v>8</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I85" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K85">
         <v>5000</v>
@@ -4152,15 +4176,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4172,10 +4196,10 @@
         <v>8</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I86" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K86">
         <v>5000</v>
@@ -4184,15 +4208,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4204,15 +4228,47 @@
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I87" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K87">
         <v>5000</v>
       </c>
       <c r="M87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B88">
+        <v>6035</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D88">
+        <v>5</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I88" t="s">
+        <v>285</v>
+      </c>
+      <c r="K88">
+        <v>5000</v>
+      </c>
+      <c r="M88">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCC1CA1-8962-47AA-BB1A-9B0AD9E467EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036C4209-5D83-46F5-AB89-70294C3A37F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="319">
   <si>
     <t>##var</t>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>时间币</t>
-  </si>
-  <si>
-    <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
@@ -970,6 +967,97 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>糯米</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>节日材料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[glutinous_rice]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粽叶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>清新翠绿的粽叶，轻轻折起，就能把香气和心意一起包进去</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi_leaves]</t>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>细麻绳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[hemp_cord]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾草</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[mugwort]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一束带着清香的艾草。插在门边，连路过的风都染上了端午的味道。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>粽子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>节日礼盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,200,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾草福袋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结实耐用的麻绳，负责把粽子牢牢捆好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洁白饱满的糯米，蒸熟后软软糯糯的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[sachet]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚出锅的粽子，粽叶清香与软糯米香交织，趁热最好吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>装满艾草的香囊，随身佩戴，寄托平安顺遂的美好</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1312,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="4" bestFit="1" customWidth="1"/>
@@ -1704,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="K10">
         <v>4000</v>
@@ -1721,7 +1809,7 @@
         <v>1011</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1">
         <v>3</v>
@@ -1736,10 +1824,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="K11">
         <v>4000</v>
@@ -1753,7 +1841,7 @@
         <v>1012</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
@@ -1768,10 +1856,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="K12">
         <v>3500</v>
@@ -1785,7 +1873,7 @@
         <v>1013</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -1800,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="K13">
         <v>4000</v>
@@ -1817,25 +1905,25 @@
         <v>1050</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1844,7 +1932,7 @@
         <v>4000</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1855,7 +1943,7 @@
         <v>1051</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -1864,16 +1952,16 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1882,7 +1970,7 @@
         <v>4000</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1893,7 +1981,7 @@
         <v>1052</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -1902,16 +1990,16 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1920,7 +2008,7 @@
         <v>4000</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1931,7 +2019,7 @@
         <v>2000</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="1">
         <v>3</v>
@@ -1940,16 +2028,16 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="K17">
         <v>3200</v>
@@ -1963,7 +2051,7 @@
         <v>3000</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1972,16 +2060,16 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1990,7 +2078,7 @@
         <v>6000</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -2001,7 +2089,7 @@
         <v>3001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -2010,16 +2098,16 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2028,7 +2116,7 @@
         <v>6000</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M19"/>
     </row>
@@ -2037,7 +2125,7 @@
         <v>3002</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -2046,16 +2134,16 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2064,7 +2152,7 @@
         <v>6000</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M20"/>
     </row>
@@ -2073,7 +2161,7 @@
         <v>3010</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -2082,16 +2170,16 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2100,7 +2188,7 @@
         <v>6000</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -2111,7 +2199,7 @@
         <v>3011</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -2120,16 +2208,16 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>3</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2138,7 +2226,7 @@
         <v>6000</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M22"/>
     </row>
@@ -2147,7 +2235,7 @@
         <v>3012</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -2156,16 +2244,16 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2174,7 +2262,7 @@
         <v>6000</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -2185,7 +2273,7 @@
         <v>3020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -2194,16 +2282,16 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2212,7 +2300,7 @@
         <v>6000</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -2223,7 +2311,7 @@
         <v>3030</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -2232,16 +2320,16 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2250,7 +2338,7 @@
         <v>6000</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2258,92 +2346,100 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26">
-        <v>4000</v>
+        <v>3100</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="D26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26">
-        <v>4</v>
+        <v>309</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>109</v>
+        <v>317</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>110</v>
+        <v>310</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>4000</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M26"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>4001</v>
+        <v>3101</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>111</v>
+        <v>312</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G27">
-        <v>4</v>
+        <v>309</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>112</v>
+        <v>318</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>113</v>
+        <v>316</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>4000</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="M27"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D28" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G28">
         <v>4</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K28">
         <v>4000</v>
@@ -2352,12 +2448,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -2366,16 +2462,16 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G29">
         <v>4</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K29">
         <v>4000</v>
@@ -2386,28 +2482,28 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30">
         <v>4</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K30">
         <v>4000</v>
@@ -2416,33 +2512,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G31">
         <v>4</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I31" t="s">
-        <v>125</v>
+        <v>117</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="K31">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2450,31 +2546,31 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G32">
         <v>4</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K32">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2482,31 +2578,31 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G33">
         <v>4</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="I33" t="s">
+        <v>124</v>
       </c>
       <c r="K33">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2514,31 +2610,31 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D34" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G34">
         <v>4</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K34">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2546,31 +2642,31 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D35" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G35">
         <v>4</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I35" t="s">
-        <v>137</v>
+        <v>129</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="K35">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2578,28 +2674,28 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G36">
         <v>4</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K36">
         <v>4000</v>
@@ -2610,28 +2706,28 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>4011</v>
+        <v>4009</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G37">
         <v>4</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="I37" t="s">
+        <v>136</v>
       </c>
       <c r="K37">
         <v>4000</v>
@@ -2642,28 +2738,28 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B38">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38">
-        <v>4</v>
+        <v>137</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G38">
         <v>4</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="K38">
         <v>4000</v>
@@ -2674,28 +2770,28 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39">
-        <v>2</v>
+        <v>140</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G39">
         <v>4</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K39">
         <v>4000</v>
@@ -2706,31 +2802,31 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G40">
         <v>4</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K40">
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2738,31 +2834,31 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G41">
         <v>4</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K41">
-        <v>4400</v>
+        <v>4000</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2770,31 +2866,31 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42">
         <v>4</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I42" t="s">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="K42">
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2802,31 +2898,31 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G43">
         <v>4</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K43">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2834,31 +2930,31 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G44">
         <v>4</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
+      </c>
+      <c r="I44" t="s">
+        <v>157</v>
       </c>
       <c r="K44">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2866,31 +2962,31 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G45">
         <v>4</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="K45">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -2898,31 +2994,31 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G46">
         <v>4</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="K46">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -2930,31 +3026,31 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G47">
         <v>4</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="K47">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -2962,28 +3058,28 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B48">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G48">
         <v>4</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K48">
         <v>4500</v>
@@ -2994,31 +3090,31 @@
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G49">
         <v>4</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="K49">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3026,31 +3122,31 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G50">
         <v>4</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="I50" t="s">
-        <v>182</v>
+        <v>174</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="K50">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3058,28 +3154,28 @@
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B51">
-        <v>4025</v>
+        <v>4023</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G51">
         <v>4</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="K51">
         <v>5000</v>
@@ -3090,31 +3186,31 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G52">
         <v>4</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>188</v>
+        <v>180</v>
+      </c>
+      <c r="I52" t="s">
+        <v>181</v>
       </c>
       <c r="K52">
-        <v>5200</v>
+        <v>5500</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3122,31 +3218,31 @@
     </row>
     <row r="53" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B53">
-        <v>4027</v>
+        <v>4025</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G53">
         <v>4</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="K53">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -3154,31 +3250,31 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B54">
-        <v>4028</v>
+        <v>4026</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="G54">
         <v>4</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="K54">
-        <v>3200</v>
+        <v>5200</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3186,31 +3282,31 @@
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B55">
-        <v>5000</v>
+        <v>4027</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K55">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3218,31 +3314,31 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B56">
-        <v>5001</v>
+        <v>4028</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="K56">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="M56">
         <v>0</v>
@@ -3250,10 +3346,10 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>5002</v>
+        <v>5000</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3262,16 +3358,16 @@
         <v>1</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G57">
         <v>5</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I57" t="s">
-        <v>205</v>
+        <v>197</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="K57">
         <v>6000</v>
@@ -3282,10 +3378,10 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B58">
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3294,19 +3390,19 @@
         <v>1</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G58">
         <v>5</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="I58" t="s">
-        <v>208</v>
+        <v>200</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="K58">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -3314,10 +3410,10 @@
     </row>
     <row r="59" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>5004</v>
+        <v>5002</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -3326,16 +3422,16 @@
         <v>1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G59">
         <v>5</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="I59" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K59">
         <v>6000</v>
@@ -3346,10 +3442,10 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3358,19 +3454,19 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G60">
         <v>5</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I60" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="K60">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -3378,28 +3474,28 @@
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>5006</v>
+        <v>5004</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G61">
         <v>5</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I61" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="K61">
         <v>6000</v>
@@ -3410,28 +3506,28 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>5100</v>
+        <v>5005</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="G62">
         <v>5</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="I62" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K62">
         <v>6000</v>
@@ -3442,28 +3538,28 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>5101</v>
+        <v>5006</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="G63">
         <v>5</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>290</v>
+        <v>215</v>
+      </c>
+      <c r="I63" t="s">
+        <v>216</v>
       </c>
       <c r="K63">
         <v>6000</v>
@@ -3474,28 +3570,28 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>5102</v>
+        <v>5100</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="F64" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G64" s="1">
-        <v>5</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>291</v>
+      <c r="I64" t="s">
+        <v>219</v>
       </c>
       <c r="K64">
         <v>6000</v>
@@ -3504,222 +3600,220 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B65">
+        <v>5101</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G65">
+        <v>5</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K65">
         <v>6000</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
+      <c r="M65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>5102</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G66" s="1">
+        <v>5</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="K66">
+        <v>6000</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>5200</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D67">
         <v>2</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G65">
-        <v>6</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="K65">
-        <v>5000</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B66">
-        <v>6001</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G66">
-        <v>6</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="K66">
-        <v>5000</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B67">
-        <v>6002</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G67">
-        <v>6</v>
+        <v>297</v>
+      </c>
+      <c r="G67" s="1">
+        <v>5</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>231</v>
+        <v>315</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
       <c r="K67">
-        <v>5000</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+      <c r="M67"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>6003</v>
+        <v>5201</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G68">
-        <v>6</v>
+        <v>297</v>
+      </c>
+      <c r="G68" s="1">
+        <v>5</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="K68">
-        <v>5000</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+      <c r="M68"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="B69">
-        <v>6004</v>
+        <v>5202</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="D69">
         <v>2</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G69">
-        <v>6</v>
+        <v>297</v>
+      </c>
+      <c r="G69" s="1">
+        <v>5</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>237</v>
+        <v>314</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="K69">
-        <v>5000</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+      <c r="M69"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="B70">
-        <v>6005</v>
+        <v>5203</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="D70">
         <v>2</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G70">
-        <v>6</v>
+        <v>297</v>
+      </c>
+      <c r="G70" s="1">
+        <v>5</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>241</v>
+        <v>306</v>
       </c>
       <c r="K70">
-        <v>5000</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+      <c r="M70"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>6006</v>
+        <v>6000</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="K71">
         <v>5000</v>
@@ -3728,30 +3822,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>6007</v>
+        <v>6001</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G72">
         <v>6</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="K72">
         <v>5000</v>
@@ -3760,30 +3854,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>6008</v>
+        <v>6002</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G73">
         <v>6</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="K73">
         <v>5000</v>
@@ -3792,30 +3886,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>6009</v>
+        <v>6003</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G74">
         <v>6</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="K74">
         <v>5000</v>
@@ -3824,30 +3918,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>6010</v>
+        <v>6004</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G75">
         <v>6</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="K75">
         <v>5000</v>
@@ -3856,30 +3950,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>6011</v>
+        <v>6005</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>2</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G76">
         <v>6</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="K76">
         <v>5000</v>
@@ -3888,30 +3982,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>6020</v>
+        <v>6006</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G77">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I77" t="s">
-        <v>272</v>
+        <v>242</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="K77">
         <v>5000</v>
@@ -3920,30 +4014,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>6021</v>
+        <v>6007</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G78">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I78" t="s">
-        <v>262</v>
+        <v>245</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="K78">
         <v>5000</v>
@@ -3952,30 +4046,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B79">
-        <v>6022</v>
+        <v>6008</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79">
         <v>2</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I79" t="s">
-        <v>264</v>
+        <v>248</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="K79">
         <v>5000</v>
@@ -3984,30 +4078,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>6023</v>
+        <v>6009</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G80">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I80" t="s">
-        <v>266</v>
+        <v>251</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="K80">
         <v>5000</v>
@@ -4018,28 +4112,28 @@
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>6024</v>
+        <v>6010</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="I81" t="s">
-        <v>268</v>
+        <v>254</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="K81">
         <v>5000</v>
@@ -4050,28 +4144,28 @@
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B82">
-        <v>6025</v>
+        <v>6011</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D82">
         <v>5</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="G82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I82" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="K82">
         <v>5000</v>
@@ -4082,10 +4176,10 @@
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4094,16 +4188,16 @@
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I83" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K83">
         <v>5000</v>
@@ -4114,28 +4208,28 @@
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>6031</v>
+        <v>6021</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="I84" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="K84">
         <v>5000</v>
@@ -4146,10 +4240,10 @@
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>6032</v>
+        <v>6022</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4158,16 +4252,16 @@
         <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="I85" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="K85">
         <v>5000</v>
@@ -4178,10 +4272,10 @@
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>6033</v>
+        <v>6023</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -4190,16 +4284,16 @@
         <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G86">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="I86" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="K86">
         <v>5000</v>
@@ -4210,10 +4304,10 @@
     </row>
     <row r="87" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B87">
-        <v>6034</v>
+        <v>6024</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D87">
         <v>4</v>
@@ -4222,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G87">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="I87" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="K87">
         <v>5000</v>
@@ -4242,10 +4336,10 @@
     </row>
     <row r="88" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B88">
-        <v>6035</v>
+        <v>6025</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D88">
         <v>5</v>
@@ -4254,21 +4348,213 @@
         <v>0</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="G88">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="I88" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="K88">
         <v>5000</v>
       </c>
       <c r="M88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B89">
+        <v>6030</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G89">
+        <v>8</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I89" t="s">
+        <v>274</v>
+      </c>
+      <c r="K89">
+        <v>5000</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B90">
+        <v>6031</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I90" t="s">
+        <v>276</v>
+      </c>
+      <c r="K90">
+        <v>5000</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B91">
+        <v>6032</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G91">
+        <v>8</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I91" t="s">
+        <v>278</v>
+      </c>
+      <c r="K91">
+        <v>5000</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B92">
+        <v>6033</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I92" t="s">
+        <v>280</v>
+      </c>
+      <c r="K92">
+        <v>5000</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B93">
+        <v>6034</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G93">
+        <v>8</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I93" t="s">
+        <v>282</v>
+      </c>
+      <c r="K93">
+        <v>5000</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B94">
+        <v>6035</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I94" t="s">
+        <v>284</v>
+      </c>
+      <c r="K94">
+        <v>5000</v>
+      </c>
+      <c r="M94">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -35,7 +35,6 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
@@ -445,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.125" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -514,17 +513,22 @@
           <t>canUse</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>noBatchUse</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>rewardScale</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>useEffect</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>replace</t>
         </is>
@@ -581,17 +585,22 @@
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -648,17 +657,22 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -712,20 +726,25 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>1为可在背包使用</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
+          <t>0不可使用，1普通使用，2自选宝箱</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1为不可在背包批量使用</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>奖励面板下的缩放</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>使用奖池</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>替换 Base 中的 ID</t>
         </is>
@@ -767,15 +786,18 @@
       <c r="J5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
         <v>2500</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>101,100,100</t>
         </is>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="N5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -815,15 +837,18 @@
       <c r="J6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <v>3000</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>101,300,100</t>
         </is>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="N6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -863,15 +888,18 @@
       <c r="J7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>101,1000,100</t>
         </is>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="N7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,15 +939,18 @@
       <c r="J8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>101,2000,100</t>
         </is>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="N8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -959,15 +990,18 @@
       <c r="J9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <v>3200</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>101,5000,100</t>
         </is>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="N9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1004,10 +1038,13 @@
           <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
         </is>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="N10" s="0" t="n">
         <v>102</v>
       </c>
     </row>
@@ -1044,10 +1081,13 @@
           <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
         </is>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="N11" s="0" t="n">
         <v>104</v>
       </c>
     </row>
@@ -1084,10 +1124,13 @@
           <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_secret_box_coin]</t>
         </is>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0" t="n">
         <v>3500</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="N12" s="0" t="n">
         <v>105</v>
       </c>
     </row>
@@ -1124,10 +1167,13 @@
           <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_time_core_matrix_token]</t>
         </is>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="N13" s="0" t="n">
         <v>106</v>
       </c>
     </row>
@@ -1167,15 +1213,18 @@
       <c r="J14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>103,5,100</t>
         </is>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="N14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1215,15 +1264,18 @@
       <c r="J15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>103,10,100</t>
         </is>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="N15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1263,15 +1315,18 @@
       <c r="J16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>103,15,100</t>
         </is>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="N16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1308,10 +1363,13 @@
           <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_furniture_coupon]</t>
         </is>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <v>3200</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="N17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1351,15 +1409,18 @@
       <c r="J18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="0" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>3001,1,10;4000,1,50;4001,1,50;4003,1,50;4004,1,50;4008,1,50;4009,1,50;4013,1,50;4014,1,50;4018,1,50;4019,1,50;4023,1,100</t>
         </is>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="N18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1399,15 +1460,18 @@
       <c r="J19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>3002,1,10;4002,1,50;4005,1,50;4006,1,50;4010,1,50;4011,1,50;4015,1,50;4016,1,50;4020,1,50;4021,1,50;4024,1,100</t>
         </is>
       </c>
-      <c r="M19" s="0" t="n"/>
+      <c r="N19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -1445,27 +1509,30 @@
       <c r="J20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>4007,1,50;4012,1,50;4017,1,50;4022,1,50;4025,1,100,4026,1,50;4027,1,20</t>
         </is>
       </c>
-      <c r="M20" s="0" t="n"/>
+      <c r="N20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
-        <v>3010</v>
+        <v>3003</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>低级社区物资礼盒</t>
+          <t>初级零工自选礼盒</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>1</v>
@@ -1475,135 +1542,140 @@
           <t>礼盒</t>
         </is>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="G21" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>社区给居民提交材料的回馈奖励，可以获得各种物资</t>
+          <t>可以自由选择一个初级零工所需的凭证</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_1]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_optional_box_1]</t>
         </is>
       </c>
       <c r="J21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>3011,1,10;101,100,100;1010,1,100;1011,1,10;3000,1,10</t>
-        </is>
-      </c>
-      <c r="M21" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>4000,1,100;4001,1,100;4003,1,100;4004,1,100;4008,1,100;4009,1,100;4013,1,100;4014,1,100;4018,1,100;4019,1,100;4023,1,100</t>
+        </is>
+      </c>
+      <c r="N21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
-        <v>3011</v>
+        <v>3004</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>中级社区物资礼盒</t>
+          <t>中级零工自选礼盒</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>礼盒</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>可以自由选择一个中级零工所需的凭证</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_optional_box_2]</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>礼盒</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="1" t="inlineStr">
-        <is>
-          <t>帮助社区居民获得的回馈奖励，可以获得各种物资</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_2]</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="0" t="n">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50</t>
-        </is>
-      </c>
-      <c r="M22" s="0" t="n"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>4002,1,100;4005,1,100;4006,1,100;4010,1,100;4011,1,100;4015,1,100;4016,1,100;4020,1,100;4021,1,100;4024,1,100</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
-        <v>3012</v>
+        <v>3005</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>高级社区物资礼盒</t>
+          <t>高级零工自选礼盒</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>礼盒</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>礼盒</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>3</v>
-      </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>为社区贡献卓越力量后获得的最高回馈，可以获得更丰富的物资</t>
+          <t>可以自由选择一个高级零工所需的凭证</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_3]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_optional_box_3]</t>
         </is>
       </c>
       <c r="J23" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>3001,1,55;3002,1,25;101,888,100;101,1288,100;101,1888,50;1010,3,100;1011,2,80</t>
-        </is>
-      </c>
-      <c r="M23" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>4007,1,100;4012,1,100;4017,1,100;4022,1,100;4025,1,100;4026,1,100;4027,1,100</t>
+        </is>
+      </c>
+      <c r="N23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="0" t="n">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>初级材料礼盒</t>
+          <t>低级社区物资礼盒</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
@@ -1622,7 +1694,7 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>鼓鼓的礼盒，开启有较小概率获得更高一阶的材料</t>
+          <t>社区给居民提交材料的回馈奖励，可以获得各种物资</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -1633,29 +1705,32 @@
       <c r="J24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>5000,1,100;5001,1,100;5002,1,100;5003,1,100;5004,1,100;5005,1,100;5200,1,15;5201,1,15;5202,1,15;5203,1,8;5203,2,5;5203,3,2</t>
-        </is>
-      </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>3011,1,10;101,100,100;1010,1,100;1011,1,10;3000,1,10</t>
+        </is>
+      </c>
+      <c r="N24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
-        <v>3030</v>
+        <v>3011</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>钓鱼礼盒</t>
+          <t>中级社区物资礼盒</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>1</v>
@@ -1670,36 +1745,37 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>水中的礼盒，开启可获得各式各样的道具</t>
+          <t>帮助社区居民获得的回馈奖励，可以获得各种物资</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_0]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_2]</t>
         </is>
       </c>
       <c r="J25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>101,200,100</t>
-        </is>
-      </c>
-      <c r="M25" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>101,500,100;101,888,100;1010,2,100;1011,1,50;3000,1,50</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
-        <v>3100</v>
+        <v>3012</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>粽子</t>
+          <t>高级社区物资礼盒</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
@@ -1710,136 +1786,149 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>节日礼盒</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="n">
+          <t>礼盒</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="n">
         <v>3</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>刚出锅的粽子，粽叶清香与软糯米香交织，趁热最好吃</t>
+          <t>为社区贡献卓越力量后获得的最高回馈，可以获得更丰富的物资</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_3]</t>
         </is>
       </c>
       <c r="J26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>103,5,40;103,8,40;101,100,15;101,500,5</t>
-        </is>
-      </c>
-      <c r="M26" s="0" t="n"/>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>3001,1,55;3002,1,25;101,888,100;101,1288,100;101,1888,50;1010,3,100;1011,2,80</t>
+        </is>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
-        <v>3101</v>
+        <v>3020</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>艾草福袋</t>
+          <t>初级材料礼盒</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>礼盒</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>节日礼盒</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>装满艾草的香囊，随身佩戴，寄托平安顺遂的美好</t>
+          <t>鼓鼓的礼盒，开启有较小概率获得更高一阶的材料</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[sachet]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_1]</t>
         </is>
       </c>
       <c r="J27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>101,200,100</t>
-        </is>
-      </c>
-      <c r="M27" s="0" t="n"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>5000,1,100;5001,1,100;5002,1,100;5003,1,100;5004,1,100;5005,1,100;5200,1,15;5201,1,15;5202,1,15;5203,1,8;5203,2,5;5203,3,2</t>
+        </is>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
-        <v>3102</v>
+        <v>3030</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>新春福袋</t>
+          <t>钓鱼礼盒</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>礼盒</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>节日礼盒</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>绣着吉祥纹样的福袋，装着新年第一份喜气</t>
+          <t>水中的礼盒，开启可获得各式各样的道具</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/LittleGame/SpriteAtlas.spriteatlasv2[lucky_pouch]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[gift_box_0]</t>
         </is>
       </c>
       <c r="J28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>101,200,100</t>
         </is>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="N28" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="n">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>新春红包</t>
+          <t>粽子</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
@@ -1858,116 +1947,137 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>厚实的大红包，藏着长辈沉甸甸的祝福</t>
+          <t>刚出锅的粽子，粽叶清香与软糯米香交织，趁热最好吃</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/LittleGame/SpriteAtlas.spriteatlasv2[red_envelope]</t>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi]</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>101,300,100</t>
-        </is>
-      </c>
-      <c r="M29" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>103,5,40;103,8,40;101,100,15;101,500,5</t>
+        </is>
+      </c>
+      <c r="N29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="0" t="n">
-        <v>4000</v>
+        <v>3101</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>电动踏板车</t>
+          <t>艾草福袋</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>零工</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="n">
-        <v>4</v>
+          <t>节日礼盒</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>拧下车把，城市的每条小路都能变成赚钱捷径</t>
+          <t>装满艾草的香囊，随身佩戴，寄托平安顺遂的美好</t>
         </is>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_3]</t>
-        </is>
-      </c>
-      <c r="K30" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M30" s="0" t="n">
-        <v>0</v>
-      </c>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[sachet]</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>101,200,100</t>
+        </is>
+      </c>
+      <c r="N30" s="0" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="0" t="n">
-        <v>4001</v>
+        <v>3102</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>厢式货车</t>
+          <t>新春福袋</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>零工</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="n">
-        <v>4</v>
+          <t>节日礼盒</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>装得下半座仓库</t>
+          <t>绣着吉祥纹样的福袋，装着新年第一份喜气</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_4]</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M31" s="0" t="n">
+          <t>Assets/Art/LittleGame/SpriteAtlas.spriteatlasv2[lucky_pouch]</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>101,200,100</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="n">
-        <v>4002</v>
+        <v>3103</v>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>建筑许可证书</t>
+          <t>新春红包</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
@@ -1978,36 +2088,47 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>零工</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="n">
-        <v>4</v>
+          <t>节日礼盒</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>薄薄一张纸，却能打开大型工程的厚重大门</t>
+          <t>厚实的大红包，藏着长辈沉甸甸的祝福</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_5]</t>
-        </is>
-      </c>
-      <c r="K32" s="0" t="n">
+          <t>Assets/Art/LittleGame/SpriteAtlas.spriteatlasv2[red_envelope]</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>101,300,100</t>
+        </is>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M32" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="4">
-      <c r="B33" s="0" t="n">
-        <v>4003</v>
-      </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>版式启蒙册</t>
+          <t>电动踏板车</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
@@ -2026,28 +2147,31 @@
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>教文字和图片各就各位，拯救摇摇欲坠的海报</t>
+          <t>拧下车把，城市的每条小路都能变成赚钱捷径</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_1]</t>
-        </is>
-      </c>
-      <c r="K33" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_3]</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M33" s="0" t="n">
+      <c r="N33" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="n">
-        <v>4004</v>
+        <v>4001</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>灵感数位板</t>
+          <t>厢式货车</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
@@ -2066,28 +2190,31 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>接住稍纵即逝的灵感，再把它们画成可以交稿的样子</t>
+          <t>装得下半座仓库</t>
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_2]</t>
-        </is>
-      </c>
-      <c r="K34" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_4]</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="N34" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n">
-        <v>4005</v>
+        <v>4002</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>宣传样机册</t>
+          <t>建筑许可证书</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
@@ -2106,32 +2233,35 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>提前看看成品，避免创意只活在想象之中</t>
-        </is>
-      </c>
-      <c r="I35" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_3]</t>
-        </is>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>3800</v>
-      </c>
-      <c r="M35" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
+          <t>薄薄一张纸，却能打开大型工程的厚重大门</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_5]</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N35" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="4">
       <c r="B36" s="0" t="n">
-        <v>4006</v>
+        <v>4003</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>品牌识别手册</t>
+          <t>版式启蒙册</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="0" t="n">
         <v>1</v>
@@ -2146,32 +2276,35 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>让颜色、图形和字体一眼看出是同一家人</t>
+          <t>教文字和图片各就各位，拯救摇摇欲坠的海报</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_4]</t>
-        </is>
-      </c>
-      <c r="K36" s="0" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M36" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_1]</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N36" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="n">
-        <v>4007</v>
+        <v>4004</v>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>展陈设计证</t>
+          <t>灵感数位板</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="0" t="n">
         <v>1</v>
@@ -2186,32 +2319,35 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>获得让平面创意站起来，并占满整个展厅的资格</t>
+          <t>接住稍纵即逝的灵感，再把它们画成可以交稿的样子</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_5]</t>
-        </is>
-      </c>
-      <c r="K37" s="0" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M37" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_2]</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N37" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="n">
-        <v>4008</v>
+        <v>4005</v>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Wwb三剑客教程</t>
+          <t>宣传样机册</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>1</v>
@@ -2226,32 +2362,35 @@
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>集齐结构、样式与交互，网页终于不再各长各的</t>
-        </is>
-      </c>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_1]</t>
-        </is>
-      </c>
-      <c r="K38" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M38" s="0" t="n">
+          <t>提前看看成品，避免创意只活在想象之中</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_3]</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>3800</v>
+      </c>
+      <c r="N38" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="n">
-        <v>4009</v>
+        <v>4006</v>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>WeiX教程</t>
+          <t>品牌识别手册</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>1</v>
@@ -2266,32 +2405,35 @@
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>小小页面装下大大功能</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_2]</t>
-        </is>
-      </c>
-      <c r="K39" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M39" s="0" t="n">
+          <t>让颜色、图形和字体一眼看出是同一家人</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_4]</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N39" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="n">
-        <v>4010</v>
+        <v>4007</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Hadeep教程</t>
+          <t>展陈设计证</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>1</v>
@@ -2306,32 +2448,35 @@
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>教一群机器分头搬数据</t>
+          <t>获得让平面创意站起来，并占满整个展厅的资格</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_3]</t>
-        </is>
-      </c>
-      <c r="K40" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M40" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_5]</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N40" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="n">
-        <v>4011</v>
+        <v>4008</v>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>MySOL教程</t>
+          <t>Wwb三剑客教程</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>1</v>
@@ -2346,32 +2491,35 @@
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>让四处乱跑的数据排好队</t>
+          <t>集齐结构、样式与交互，网页终于不再各长各的</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_4]</t>
-        </is>
-      </c>
-      <c r="K41" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_1]</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="N41" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="n">
-        <v>4012</v>
+        <v>4009</v>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Unlty教程</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="n">
-        <v>4</v>
+          <t>WeiX教程</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E42" s="0" t="n">
         <v>1</v>
@@ -2386,32 +2534,35 @@
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>从拖动一个方块开始，不知不觉搭出一整个世界</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_5]</t>
-        </is>
-      </c>
-      <c r="K42" s="0" t="n">
+          <t>小小页面装下大大功能</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_2]</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="N42" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="n">
-        <v>4013</v>
+        <v>4010</v>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>基础维修工具包</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="n">
-        <v>2</v>
+          <t>Hadeep教程</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E43" s="0" t="n">
         <v>1</v>
@@ -2426,32 +2577,35 @@
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>东西不算多，但足够让坏掉的家电重新反省</t>
+          <t>教一群机器分头搬数据</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_1]</t>
-        </is>
-      </c>
-      <c r="K43" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_3]</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="N43" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="n">
-        <v>4014</v>
+        <v>4011</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>管路维护套装</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>2</v>
+          <t>MySOL教程</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E44" s="0" t="n">
         <v>1</v>
@@ -2466,32 +2620,35 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>专治滴答作响，以及半夜突然有想法的水管</t>
+          <t>让四处乱跑的数据排好队</t>
         </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_2]</t>
-        </is>
-      </c>
-      <c r="K44" s="0" t="n">
-        <v>4200</v>
-      </c>
-      <c r="M44" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_4]</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N44" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="n">
-        <v>4015</v>
+        <v>4012</v>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>智能万用表</t>
+          <t>Unlty教程</t>
         </is>
       </c>
       <c r="D45" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>1</v>
@@ -2506,32 +2663,35 @@
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>电路虽然不会说话，但屏幕上的波形很会告密</t>
+          <t>从拖动一个方块开始，不知不觉搭出一整个世界</t>
         </is>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_3]</t>
-        </is>
-      </c>
-      <c r="K45" s="0" t="n">
-        <v>4400</v>
-      </c>
-      <c r="M45" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_5]</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N45" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="n">
-        <v>4016</v>
+        <v>4013</v>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>重型检修箱</t>
+          <t>基础维修工具包</t>
         </is>
       </c>
       <c r="D46" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="0" t="n">
         <v>1</v>
@@ -2546,32 +2706,35 @@
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>拧紧螺丝已经不够，让整台设备重新升级</t>
-        </is>
-      </c>
-      <c r="I46" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_4]</t>
-        </is>
-      </c>
-      <c r="K46" s="0" t="n">
+          <t>东西不算多，但足够让坏掉的家电重新反省</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_1]</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0" t="n">
         <v>4000</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="N46" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="n">
-        <v>4017</v>
+        <v>4014</v>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>精密校准箱</t>
+          <t>管路维护套装</t>
         </is>
       </c>
       <c r="D47" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>1</v>
@@ -2586,32 +2749,35 @@
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>专门处理肉眼看不见、维修报价却看得很清楚的问题</t>
+          <t>专治滴答作响，以及半夜突然有想法的水管</t>
         </is>
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_5]</t>
-        </is>
-      </c>
-      <c r="K47" s="0" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M47" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_2]</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <v>4200</v>
+      </c>
+      <c r="N47" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="n">
-        <v>4018</v>
+        <v>4015</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>灵感钢笔</t>
+          <t>智能万用表</t>
         </is>
       </c>
       <c r="D48" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" s="0" t="n">
         <v>1</v>
@@ -2626,32 +2792,35 @@
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>负责把路过脑海的句子当场逮住，并按在纸上</t>
+          <t>电路虽然不会说话，但屏幕上的波形很会告密</t>
         </is>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_1]</t>
-        </is>
-      </c>
-      <c r="K48" s="0" t="n">
-        <v>5500</v>
-      </c>
-      <c r="M48" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_3]</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <v>4400</v>
+      </c>
+      <c r="N48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="n">
-        <v>4019</v>
+        <v>4016</v>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>卖点卡册</t>
+          <t>重型检修箱</t>
         </is>
       </c>
       <c r="D49" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="0" t="n">
         <v>1</v>
@@ -2666,32 +2835,35 @@
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>普通东西翻上几页，也能发现自己其实很有优势</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_2]</t>
-        </is>
-      </c>
-      <c r="K49" s="0" t="n">
-        <v>5500</v>
-      </c>
-      <c r="M49" s="0" t="n">
+          <t>拧紧螺丝已经不够，让整台设备重新升级</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_4]</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="n">
-        <v>4020</v>
+        <v>4017</v>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>采访录音笔</t>
+          <t>精密校准箱</t>
         </is>
       </c>
       <c r="D50" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>1</v>
@@ -2706,32 +2878,35 @@
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>忠实记录每句话，包括那句“这段千万别写”</t>
+          <t>专门处理肉眼看不见、维修报价却看得很清楚的问题</t>
         </is>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_3]</t>
-        </is>
-      </c>
-      <c r="K50" s="0" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M50" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_5]</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <v>4000</v>
+      </c>
+      <c r="N50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="n">
-        <v>4021</v>
+        <v>4018</v>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>剧本打字机</t>
+          <t>灵感钢笔</t>
         </is>
       </c>
       <c r="D51" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>1</v>
@@ -2746,32 +2921,35 @@
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>纸上的人物开始互相制造麻烦</t>
+          <t>负责把路过脑海的句子当场逮住，并按在纸上</t>
         </is>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_4]</t>
-        </is>
-      </c>
-      <c r="K51" s="0" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M51" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_1]</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="0" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="n">
-        <v>4022</v>
+        <v>4019</v>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>策划档案箱</t>
+          <t>卖点卡册</t>
         </is>
       </c>
       <c r="D52" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>1</v>
@@ -2786,32 +2964,35 @@
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>装得下目标、流程和预算</t>
+          <t>普通东西翻上几页，也能发现自己其实很有优势</t>
         </is>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_5]</t>
-        </is>
-      </c>
-      <c r="K52" s="0" t="n">
-        <v>4500</v>
-      </c>
-      <c r="M52" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_2]</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="0" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="n">
-        <v>4023</v>
+        <v>4020</v>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>临时委托单</t>
+          <t>采访录音笔</t>
         </is>
       </c>
       <c r="D53" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>1</v>
@@ -2826,28 +3007,31 @@
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>一张突然送上门的工作，撕下票根就没有犹豫时间</t>
+          <t>忠实记录每句话，包括那句“这段千万别写”</t>
         </is>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_1]</t>
-        </is>
-      </c>
-      <c r="K53" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M53" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_3]</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N53" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="n">
-        <v>4024</v>
+        <v>4021</v>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>合作通行券</t>
+          <t>剧本打字机</t>
         </is>
       </c>
       <c r="D54" s="0" t="n">
@@ -2866,28 +3050,31 @@
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>有效期和机会一样短暂，验票之后立即失效</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_2]</t>
-        </is>
-      </c>
-      <c r="K54" s="0" t="n">
-        <v>5500</v>
-      </c>
-      <c r="M54" s="0" t="n">
+          <t>纸上的人物开始互相制造麻烦</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_4]</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N54" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="0" t="n">
-        <v>4025</v>
+        <v>4022</v>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>特别邀请函</t>
+          <t>策划档案箱</t>
         </is>
       </c>
       <c r="D55" s="0" t="n">
@@ -2906,32 +3093,35 @@
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>看起来不像群发的，至少封蜡盖得非常认真</t>
+          <t>装得下目标、流程和预算</t>
         </is>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_3]</t>
-        </is>
-      </c>
-      <c r="K55" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M55" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_5]</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="0" t="n">
+        <v>4500</v>
+      </c>
+      <c r="N55" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="0" t="n">
-        <v>4026</v>
+        <v>4023</v>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>项目投标书</t>
+          <t>临时委托单</t>
         </is>
       </c>
       <c r="D56" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="0" t="n">
         <v>1</v>
@@ -2946,32 +3136,35 @@
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>把准备与野心装订成册，提交后静候命运翻页</t>
+          <t>一张突然送上门的工作，撕下票根就没有犹豫时间</t>
         </is>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_4]</t>
-        </is>
-      </c>
-      <c r="K56" s="0" t="n">
-        <v>5200</v>
-      </c>
-      <c r="M56" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_1]</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N56" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="n">
-        <v>4027</v>
+        <v>4024</v>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>传奇推荐信</t>
+          <t>合作通行券</t>
         </is>
       </c>
       <c r="D57" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E57" s="0" t="n">
         <v>1</v>
@@ -2986,39 +3179,42 @@
       </c>
       <c r="H57" s="1" t="inlineStr">
         <is>
-          <t>有人替你敲开命运的大门，可惜这封信只能用一次</t>
-        </is>
-      </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
-        </is>
-      </c>
-      <c r="K57" s="0" t="n">
+          <t>有效期和机会一样短暂，验票之后立即失效</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_2]</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="0" t="n">
         <v>5500</v>
       </c>
-      <c r="M57" s="0" t="n">
+      <c r="N57" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="n">
-        <v>4028</v>
+        <v>4025</v>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>地铁卡</t>
+          <t>特别邀请函</t>
         </is>
       </c>
       <c r="D58" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>地铁站</t>
+          <t>零工</t>
         </is>
       </c>
       <c r="G58" s="0" t="n">
@@ -3026,148 +3222,160 @@
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>有了这张卡，就可以去你想去的地方</t>
+          <t>看起来不像群发的，至少封蜡盖得非常认真</t>
         </is>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[time_chip_metro_card]</t>
-        </is>
-      </c>
-      <c r="K58" s="0" t="n">
-        <v>3200</v>
-      </c>
-      <c r="M58" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_3]</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N58" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="n">
-        <v>5000</v>
+        <v>4026</v>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>野生狗奶</t>
+          <t>项目投标书</t>
         </is>
       </c>
       <c r="D59" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>零工</t>
         </is>
       </c>
       <c r="G59" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>一切秩序即将崩塌，宇宙论为一片死寂虚空，而野生狗奶依旧存在</t>
+          <t>把准备与野心装订成册，提交后静候命运翻页</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_wild_dog_milk]</t>
-        </is>
-      </c>
-      <c r="K59" s="0" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M59" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_4]</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="0" t="n">
+        <v>5200</v>
+      </c>
+      <c r="N59" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="0" t="n">
-        <v>5001</v>
+        <v>4027</v>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>活虾(死亡)</t>
+          <t>传奇推荐信</t>
         </is>
       </c>
       <c r="D60" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E60" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>零工</t>
         </is>
       </c>
       <c r="G60" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>量子叠加，薛定谔的终极定理，超出三界之外，不在五行之中，售价十四</t>
+          <t>有人替你敲开命运的大门，可惜这封信只能用一次</t>
         </is>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_live_shrimp(dead)]</t>
-        </is>
-      </c>
-      <c r="K60" s="0" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M60" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="0" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N60" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="0" t="n">
-        <v>5002</v>
+        <v>4028</v>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>免费米饭</t>
+          <t>地铁卡</t>
         </is>
       </c>
       <c r="D61" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>材料</t>
+          <t>地铁站</t>
         </is>
       </c>
       <c r="G61" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>最后的考古学家在虚空尽头挖出一块牌子，写着：”免费米饭，两元"</t>
-        </is>
-      </c>
-      <c r="I61" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_free_rice_two_yuan]</t>
-        </is>
-      </c>
-      <c r="K61" s="0" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M61" s="0" t="n">
+          <t>有了这张卡，就可以去你想去的地方</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[time_chip_metro_card]</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="0" t="n">
+        <v>3200</v>
+      </c>
+      <c r="N61" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="n">
-        <v>5003</v>
+        <v>5000</v>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>春秋肠</t>
+          <t>野生狗奶</t>
         </is>
       </c>
       <c r="D62" s="0" t="n">
@@ -3186,28 +3394,31 @@
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>吃下它，你将重新站在那个岔路口，再一次，做出同样的选择</t>
-        </is>
-      </c>
-      <c r="I62" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_spring_autumn_ham]</t>
-        </is>
-      </c>
-      <c r="K62" s="0" t="n">
-        <v>7000</v>
-      </c>
-      <c r="M62" s="0" t="n">
+          <t>一切秩序即将崩塌，宇宙论为一片死寂虚空，而野生狗奶依旧存在</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_wild_dog_milk]</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N62" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="0" t="n">
-        <v>5004</v>
+        <v>5001</v>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>小鸡手办</t>
+          <t>活虾(死亡)</t>
         </is>
       </c>
       <c r="D63" s="0" t="n">
@@ -3226,28 +3437,31 @@
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>似曾相识故人来</t>
-        </is>
-      </c>
-      <c r="I63" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_basketball_trainee_chicken]</t>
-        </is>
-      </c>
-      <c r="K63" s="0" t="n">
+          <t>量子叠加，薛定谔的终极定理，超出三界之外，不在五行之中，售价十四</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_live_shrimp(dead)]</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M63" s="0" t="n">
+      <c r="N63" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="n">
-        <v>5005</v>
+        <v>5002</v>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>小鱼干</t>
+          <t>免费米饭</t>
         </is>
       </c>
       <c r="D64" s="0" t="n">
@@ -3266,32 +3480,35 @@
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>是猫猫最喜欢的食物</t>
+          <t>最后的考古学家在虚空尽头挖出一块牌子，写着：”免费米饭，两元"</t>
         </is>
       </c>
       <c r="I64" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[item_dried_fish]</t>
-        </is>
-      </c>
-      <c r="K64" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_free_rice_two_yuan]</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M64" s="0" t="n">
+      <c r="N64" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="n">
-        <v>5006</v>
+        <v>5003</v>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>超长长长蛋挞</t>
+          <t>春秋肠</t>
         </is>
       </c>
       <c r="D65" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="0" t="n">
         <v>1</v>
@@ -3306,39 +3523,42 @@
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>60cm巨无霸，超长长长长长长长长长长长长蛋挞！</t>
+          <t>吃下它，你将重新站在那个岔路口，再一次，做出同样的选择</t>
         </is>
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[item_extra_long_egg_tart]</t>
-        </is>
-      </c>
-      <c r="K65" s="0" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M65" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_spring_autumn_ham]</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="0" t="n">
+        <v>7000</v>
+      </c>
+      <c r="N65" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="0" t="n">
-        <v>5100</v>
+        <v>5004</v>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>草莓小熊</t>
+          <t>小鸡手办</t>
         </is>
       </c>
       <c r="D66" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>稀有材料</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="G66" s="0" t="n">
@@ -3346,39 +3566,42 @@
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>女儿一直想要的草莓小熊，为什么会从河里钓起来?</t>
+          <t>似曾相识故人来</t>
         </is>
       </c>
       <c r="I66" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_pink_bear_plush_icon]</t>
-        </is>
-      </c>
-      <c r="K66" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_basketball_trainee_chicken]</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M66" s="0" t="n">
+      <c r="N66" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="0" t="n">
-        <v>5101</v>
+        <v>5005</v>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>海洋之心</t>
+          <t>小鱼干</t>
         </is>
       </c>
       <c r="D67" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>稀有材料</t>
+          <t>材料</t>
         </is>
       </c>
       <c r="G67" s="0" t="n">
@@ -3386,156 +3609,171 @@
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>完美的吊坠，送给喵夫人最为合适了</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
-        </is>
-      </c>
-      <c r="K67" s="0" t="n">
+          <t>是猫猫最喜欢的食物</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[item_dried_fish]</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M67" s="0" t="n">
+      <c r="N67" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="n">
-        <v>5102</v>
+        <v>5006</v>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>强力胶带</t>
+          <t>超长长长蛋挞</t>
         </is>
       </c>
       <c r="D68" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>任务道具</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="n">
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="n">
         <v>5</v>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>熊大山需要的强力胶带，快交给他吧!</t>
-        </is>
-      </c>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[dream_city_strong_duct_tape_icon]</t>
-        </is>
-      </c>
-      <c r="K68" s="0" t="n">
+          <t>60cm巨无霸，超长长长长长长长长长长长长蛋挞！</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[item_extra_long_egg_tart]</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M68" s="0" t="n">
+      <c r="N68" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="0" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>糯米</t>
+          <t>草莓小熊</t>
         </is>
       </c>
       <c r="D69" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E69" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>节日材料</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="n">
+          <t>稀有材料</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="n">
         <v>5</v>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>洁白饱满的糯米，蒸熟后软软糯糯的</t>
-        </is>
-      </c>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[glutinous_rice]</t>
-        </is>
-      </c>
-      <c r="K69" s="0" t="n">
+          <t>女儿一直想要的草莓小熊，为什么会从河里钓起来?</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_pink_bear_plush_icon]</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M69" s="0" t="n"/>
+      <c r="N69" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="0" t="n">
-        <v>5201</v>
+        <v>5101</v>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>粽叶</t>
+          <t>海洋之心</t>
         </is>
       </c>
       <c r="D70" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E70" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>节日材料</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="n">
+          <t>稀有材料</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="n">
         <v>5</v>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>清新翠绿的粽叶，轻轻折起，就能把香气和心意一起包进去</t>
+          <t>完美的吊坠，送给喵夫人最为合适了</t>
         </is>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi_leaves]</t>
-        </is>
-      </c>
-      <c r="K70" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[rare_ocean_heart_pendant_icon]</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M70" s="0" t="n"/>
+      <c r="N70" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="0" t="n"/>
       <c r="B71" s="0" t="n">
-        <v>5202</v>
+        <v>5102</v>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>麻绳</t>
+          <t>强力胶带</t>
         </is>
       </c>
       <c r="D71" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>节日材料</t>
+          <t>任务道具</t>
         </is>
       </c>
       <c r="G71" s="1" t="n">
@@ -3543,27 +3781,31 @@
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>结实耐用的麻绳，负责把粽子牢牢捆好</t>
+          <t>熊大山需要的强力胶带，快交给他吧!</t>
         </is>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[hemp_cord]</t>
-        </is>
-      </c>
-      <c r="K71" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[dream_city_strong_duct_tape_icon]</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M71" s="0" t="n"/>
+      <c r="N71" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="0" t="n"/>
       <c r="B72" s="0" t="n">
-        <v>5203</v>
+        <v>5200</v>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>艾草</t>
+          <t>糯米</t>
         </is>
       </c>
       <c r="D72" s="0" t="n">
@@ -3582,150 +3824,158 @@
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>一束带着清香的艾草。插在门边，连路过的风都染上了端午的味道。</t>
+          <t>洁白饱满的糯米，蒸熟后软软糯糯的</t>
         </is>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[mugwort]</t>
-        </is>
-      </c>
-      <c r="K72" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[glutinous_rice]</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="M72" s="0" t="n"/>
+      <c r="N72" s="0" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="0" t="n">
+        <v>5201</v>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>粽叶</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>节日材料</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>清新翠绿的粽叶，轻轻折起，就能把香气和心意一起包进去</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[zongzi_leaves]</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="0" t="n">
         <v>6000</v>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>小白条</t>
-        </is>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="0" t="n">
+      <c r="N73" s="0" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n"/>
+      <c r="B74" s="0" t="n">
+        <v>5202</v>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>麻绳</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>鱼获</t>
-        </is>
-      </c>
-      <c r="G73" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>总爱成群贴着水面穿梭，个头不大，逃跑时倒是格外认真</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_01_white_strip]</t>
-        </is>
-      </c>
-      <c r="K73" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M73" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="0" t="n">
-        <v>6001</v>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>河鲫鱼</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="E74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>节日材料</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>结实耐用的麻绳，负责把粽子牢牢捆好</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[hemp_cord]</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N74" s="0" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n"/>
+      <c r="B75" s="0" t="n">
+        <v>5203</v>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>艾草</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>鱼获</t>
-        </is>
-      </c>
-      <c r="G74" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H74" s="1" t="inlineStr">
-        <is>
-          <t>河畔最常见的老住户，性情温和，似乎已经看惯了岸边的钓鱼人</t>
-        </is>
-      </c>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_02_crucian]</t>
-        </is>
-      </c>
-      <c r="K74" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M74" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="0" t="n">
-        <v>6002</v>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>小泥鳅</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="E75" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>鱼获</t>
-        </is>
-      </c>
-      <c r="G75" s="0" t="n">
-        <v>6</v>
+          <t>节日材料</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>身体滑溜得几乎抓不住，一眨眼就能钻进河底的泥沙里</t>
+          <t>一束带着清香的艾草。插在门边，连路过的风都染上了端午的味道。</t>
         </is>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_03_loach]</t>
-        </is>
-      </c>
-      <c r="K75" s="0" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M75" s="0" t="n">
-        <v>0</v>
-      </c>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[mugwort]</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="0" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N75" s="0" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="0" t="n">
-        <v>6003</v>
+        <v>6000</v>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>红尾鲤鱼</t>
+          <t>小白条</t>
         </is>
       </c>
       <c r="D76" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="0" t="n">
         <v>2</v>
@@ -3740,32 +3990,35 @@
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>摆动鲜艳的红色尾鳍缓缓游过，据说遇见它会带来一点小好运</t>
+          <t>总爱成群贴着水面穿梭，个头不大，逃跑时倒是格外认真</t>
         </is>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_04_redtail_carp]</t>
-        </is>
-      </c>
-      <c r="K76" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_01_white_strip]</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M76" s="0" t="n">
+      <c r="N76" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>青草鱼</t>
+          <t>河鲫鱼</t>
         </is>
       </c>
       <c r="D77" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="0" t="n">
         <v>2</v>
@@ -3780,32 +4033,35 @@
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>喜欢藏在水草丰茂的地方，胃口很好，几乎从不浪费任何一片嫩叶</t>
+          <t>河畔最常见的老住户，性情温和，似乎已经看惯了岸边的钓鱼人</t>
         </is>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_05_grass_carp]</t>
-        </is>
-      </c>
-      <c r="K77" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_02_crucian]</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M77" s="0" t="n">
+      <c r="N77" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="n">
-        <v>6005</v>
+        <v>6002</v>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>银鲢鱼</t>
+          <t>小泥鳅</t>
         </is>
       </c>
       <c r="D78" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="0" t="n">
         <v>2</v>
@@ -3820,32 +4076,35 @@
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>银亮的鱼身会映出水面的天光，受到惊吓时常会突然跃出水面</t>
+          <t>身体滑溜得几乎抓不住，一眨眼就能钻进河底的泥沙里</t>
         </is>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_06_silver_carp]</t>
-        </is>
-      </c>
-      <c r="K78" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_03_loach]</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M78" s="0" t="n">
+      <c r="N78" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="0" t="n">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>河鲈鱼</t>
+          <t>红尾鲤鱼</t>
         </is>
       </c>
       <c r="D79" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="0" t="n">
         <v>2</v>
@@ -3860,32 +4119,35 @@
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>披着整齐的深色条纹，是河中敏捷的猎手，上钩后依然很有力气</t>
+          <t>摆动鲜艳的红色尾鳍缓缓游过，据说遇见它会带来一点小好运</t>
         </is>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_07_river_perch]</t>
-        </is>
-      </c>
-      <c r="K79" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_04_redtail_carp]</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M79" s="0" t="n">
+      <c r="N79" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="0" t="n">
-        <v>6007</v>
+        <v>6004</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>花鳜鱼</t>
+          <t>青草鱼</t>
         </is>
       </c>
       <c r="D80" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" s="0" t="n">
         <v>2</v>
@@ -3900,32 +4162,35 @@
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>华丽斑纹是天然的伪装，静止时几乎能与河底的碎石融为一体</t>
+          <t>喜欢藏在水草丰茂的地方，胃口很好，几乎从不浪费任何一片嫩叶</t>
         </is>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_08_mandarin_fish]</t>
-        </is>
-      </c>
-      <c r="K80" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_05_grass_carp]</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M80" s="0" t="n">
+      <c r="N80" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="n">
-        <v>6008</v>
+        <v>6005</v>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>蓝须鲶鱼</t>
+          <t>银鲢鱼</t>
         </is>
       </c>
       <c r="D81" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="0" t="n">
         <v>2</v>
@@ -3940,32 +4205,35 @@
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>长长的胡须可以感知水流变化，即使在昏暗的河底也不会迷路</t>
+          <t>银亮的鱼身会映出水面的天光，受到惊吓时常会突然跃出水面</t>
         </is>
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_09_blue_catfish]</t>
-        </is>
-      </c>
-      <c r="K81" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_06_silver_carp]</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M81" s="0" t="n">
+      <c r="N81" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="n">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>福运锦鲤</t>
+          <t>河鲈鱼</t>
         </is>
       </c>
       <c r="D82" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="0" t="n">
         <v>2</v>
@@ -3980,32 +4248,35 @@
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>白橙相间的鳞片十分耀眼，传说放进水缸里，家中的好运会悄悄增加</t>
+          <t>披着整齐的深色条纹，是河中敏捷的猎手，上钩后依然很有力气</t>
         </is>
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_10_lucky_koi]</t>
-        </is>
-      </c>
-      <c r="K82" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_07_river_perch]</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M82" s="0" t="n">
+      <c r="N82" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="n">
-        <v>6010</v>
+        <v>6007</v>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>月辉鳟鱼</t>
+          <t>花鳜鱼</t>
         </is>
       </c>
       <c r="D83" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="0" t="n">
         <v>2</v>
@@ -4020,32 +4291,35 @@
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>只在月光洒满河面时出现，游过之后，水中会留下一道淡淡的银蓝微光</t>
+          <t>华丽斑纹是天然的伪装，静止时几乎能与河底的碎石融为一体</t>
         </is>
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_11_moonlight_trout]</t>
-        </is>
-      </c>
-      <c r="K83" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_08_mandarin_fish]</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M83" s="0" t="n">
+      <c r="N83" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>时光游鱼</t>
+          <t>蓝须鲶鱼</t>
         </is>
       </c>
       <c r="D84" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E84" s="0" t="n">
         <v>2</v>
@@ -4060,152 +4334,164 @@
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>鳞片间流动着细小的时间刻度，据说凝视它太久，会想起一段已经遗忘的往事</t>
+          <t>长长的胡须可以感知水流变化，即使在昏暗的河底也不会迷路</t>
         </is>
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_12_timefish]</t>
-        </is>
-      </c>
-      <c r="K84" s="0" t="n">
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_09_blue_catfish]</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M84" s="0" t="n">
+      <c r="N84" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="n">
-        <v>6020</v>
+        <v>6009</v>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>练习圆钩</t>
+          <t>福运锦鲤</t>
         </is>
       </c>
       <c r="D85" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>鱼钩</t>
+          <t>鱼获</t>
         </is>
       </c>
       <c r="G85" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>练习圆钩</t>
-        </is>
-      </c>
-      <c r="I85" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_01_beginner]</t>
-        </is>
-      </c>
-      <c r="K85" s="0" t="n">
+          <t>白橙相间的鳞片十分耀眼，传说放进水缸里，家中的好运会悄悄增加</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_10_lucky_koi]</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M85" s="0" t="n">
+      <c r="N85" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="n">
-        <v>6021</v>
+        <v>6010</v>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>灵巧细钩</t>
+          <t>月辉鳟鱼</t>
         </is>
       </c>
       <c r="D86" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>鱼钩</t>
+          <t>鱼获</t>
         </is>
       </c>
       <c r="G86" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>灵巧细钩</t>
-        </is>
-      </c>
-      <c r="I86" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_02_agile]</t>
-        </is>
-      </c>
-      <c r="K86" s="0" t="n">
+          <t>只在月光洒满河面时出现，游过之后，水中会留下一道淡淡的银蓝微光</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_11_moonlight_trout]</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M86" s="0" t="n">
+      <c r="N86" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="n">
-        <v>6022</v>
+        <v>6011</v>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>宽口鱼钩</t>
+          <t>时光游鱼</t>
         </is>
       </c>
       <c r="D87" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>鱼钩</t>
+          <t>鱼获</t>
         </is>
       </c>
       <c r="G87" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>宽口鱼钩</t>
-        </is>
-      </c>
-      <c r="I87" s="0" t="inlineStr">
-        <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_03_wide]</t>
-        </is>
-      </c>
-      <c r="K87" s="0" t="n">
+          <t>鳞片间流动着细小的时间刻度，据说凝视它太久，会想起一段已经遗忘的往事</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_12_timefish]</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M87" s="0" t="n">
+      <c r="N87" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="n">
-        <v>6023</v>
+        <v>6020</v>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>稳固倒刺钩</t>
+          <t>练习圆钩</t>
         </is>
       </c>
       <c r="D88" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" s="0" t="n">
         <v>0</v>
@@ -4220,32 +4506,35 @@
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>稳固倒刺钩</t>
+          <t>练习圆钩</t>
         </is>
       </c>
       <c r="I88" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_04_barbed]</t>
-        </is>
-      </c>
-      <c r="K88" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_01_beginner]</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M88" s="0" t="n">
+      <c r="N88" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="n">
-        <v>6024</v>
+        <v>6021</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>双重稳固钩</t>
+          <t>灵巧细钩</t>
         </is>
       </c>
       <c r="D89" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="0" t="n">
         <v>0</v>
@@ -4260,32 +4549,35 @@
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>双重稳固钩</t>
+          <t>灵巧细钩</t>
         </is>
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_05_double]</t>
-        </is>
-      </c>
-      <c r="K89" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_02_agile]</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M89" s="0" t="n">
+      <c r="N89" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="n">
-        <v>6025</v>
+        <v>6022</v>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>时光鱼钩</t>
+          <t>宽口鱼钩</t>
         </is>
       </c>
       <c r="D90" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E90" s="0" t="n">
         <v>0</v>
@@ -4300,152 +4592,164 @@
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>时光鱼钩</t>
+          <t>宽口鱼钩</t>
         </is>
       </c>
       <c r="I90" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_06_time]</t>
-        </is>
-      </c>
-      <c r="K90" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_03_wide]</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M90" s="0" t="n">
+      <c r="N90" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="n">
-        <v>6030</v>
+        <v>6023</v>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>面团</t>
+          <t>稳固倒刺钩</t>
         </is>
       </c>
       <c r="D91" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>鱼饵</t>
+          <t>鱼钩</t>
         </is>
       </c>
       <c r="G91" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>面团</t>
+          <t>稳固倒刺钩</t>
         </is>
       </c>
       <c r="I91" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_dough]</t>
-        </is>
-      </c>
-      <c r="K91" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_04_barbed]</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M91" s="0" t="n">
+      <c r="N91" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="n">
-        <v>6031</v>
+        <v>6024</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>蚯蚓</t>
+          <t>双重稳固钩</t>
         </is>
       </c>
       <c r="D92" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>鱼饵</t>
+          <t>鱼钩</t>
         </is>
       </c>
       <c r="G92" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>蚯蚓</t>
+          <t>双重稳固钩</t>
         </is>
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_worm]</t>
-        </is>
-      </c>
-      <c r="K92" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_05_double]</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M92" s="0" t="n">
+      <c r="N92" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="n">
-        <v>6032</v>
+        <v>6025</v>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>时光鱼钩</t>
         </is>
       </c>
       <c r="D93" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E93" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>鱼饵</t>
+          <t>鱼钩</t>
         </is>
       </c>
       <c r="G93" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>时光鱼钩</t>
         </is>
       </c>
       <c r="I93" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_corn]</t>
-        </is>
-      </c>
-      <c r="K93" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_hook_06_time]</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M93" s="0" t="n">
+      <c r="N93" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="n">
-        <v>6033</v>
+        <v>6030</v>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>小虾</t>
+          <t>面团</t>
         </is>
       </c>
       <c r="D94" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="0" t="n">
         <v>0</v>
@@ -4460,32 +4764,35 @@
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>小虾</t>
+          <t>面团</t>
         </is>
       </c>
       <c r="I94" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_shrimp]</t>
-        </is>
-      </c>
-      <c r="K94" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_dough]</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M94" s="0" t="n">
+      <c r="N94" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="n">
-        <v>6034</v>
+        <v>6031</v>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>紫金果</t>
+          <t>蚯蚓</t>
         </is>
       </c>
       <c r="D95" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E95" s="0" t="n">
         <v>0</v>
@@ -4500,32 +4807,35 @@
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>紫金果</t>
+          <t>蚯蚓</t>
         </is>
       </c>
       <c r="I95" s="0" t="inlineStr">
         <is>
-          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_scent_fruit]</t>
-        </is>
-      </c>
-      <c r="K95" s="0" t="n">
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_worm]</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M95" s="0" t="n">
+      <c r="N95" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="0" t="n">
-        <v>6035</v>
+        <v>6032</v>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>时光果</t>
+          <t>玉米</t>
         </is>
       </c>
       <c r="D96" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" s="0" t="n">
         <v>0</v>
@@ -4540,18 +4850,150 @@
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
+          <t>玉米</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_corn]</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N96" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="0" t="n">
+        <v>6033</v>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>小虾</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>鱼饵</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>小虾</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_shrimp]</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N97" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="0" t="n">
+        <v>6034</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>紫金果</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>鱼饵</t>
+        </is>
+      </c>
+      <c r="G98" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>紫金果</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_scent_fruit]</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="0" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N98" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="0" t="n">
+        <v>6035</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
           <t>时光果</t>
         </is>
       </c>
-      <c r="I96" s="0" t="inlineStr">
+      <c r="D99" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>鱼饵</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>时光果</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
         <is>
           <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[fishing_bait_time]</t>
         </is>
       </c>
-      <c r="K96" s="0" t="n">
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="0" t="n">
         <v>5000</v>
       </c>
-      <c r="M96" s="0" t="n">
+      <c r="N99" s="0" t="n">
         <v>0</v>
       </c>
     </row>
